--- a/database/db/prueba5_registros_CRCSC.xlsx
+++ b/database/db/prueba5_registros_CRCSC.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$447</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3137" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="922">
   <si>
     <t>company_id</t>
   </si>
@@ -1170,9 +1173,6 @@
   </si>
   <si>
     <t>GENERICO4854</t>
-  </si>
-  <si>
-    <t>RECHAZADA</t>
   </si>
   <si>
     <t>CRSC112984</t>
@@ -9364,9 +9364,7 @@
       <c r="L178">
         <v>308754</v>
       </c>
-      <c r="M178" s="8" t="s">
-        <v>381</v>
-      </c>
+      <c r="M178" s="8"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" t="s">
@@ -9385,17 +9383,15 @@
         <v>16</v>
       </c>
       <c r="J179" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="K179" s="7" t="s">
         <v>382</v>
-      </c>
-      <c r="K179" s="7" t="s">
-        <v>383</v>
       </c>
       <c r="L179">
         <v>308754</v>
       </c>
-      <c r="M179" s="8" t="s">
-        <v>381</v>
-      </c>
+      <c r="M179" s="8"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" t="s">
@@ -9405,19 +9401,19 @@
         <v>13</v>
       </c>
       <c r="C180" t="s">
+        <v>383</v>
+      </c>
+      <c r="D180" t="s">
+        <v>15</v>
+      </c>
+      <c r="F180" t="s">
+        <v>16</v>
+      </c>
+      <c r="J180" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="D180" t="s">
-        <v>15</v>
-      </c>
-      <c r="F180" t="s">
-        <v>16</v>
-      </c>
-      <c r="J180" s="12" t="s">
+      <c r="K180" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="K180" s="7" t="s">
-        <v>386</v>
       </c>
       <c r="L180">
         <v>214000</v>
@@ -9434,7 +9430,7 @@
         <v>13</v>
       </c>
       <c r="C181" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D181" t="s">
         <v>15</v>
@@ -9443,10 +9439,10 @@
         <v>16</v>
       </c>
       <c r="J181" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="K181" s="7" t="s">
         <v>387</v>
-      </c>
-      <c r="K181" s="7" t="s">
-        <v>388</v>
       </c>
       <c r="L181">
         <v>149800</v>
@@ -9463,7 +9459,7 @@
         <v>13</v>
       </c>
       <c r="C182" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D182" t="s">
         <v>15</v>
@@ -9472,10 +9468,10 @@
         <v>16</v>
       </c>
       <c r="J182" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="K182" s="7" t="s">
         <v>389</v>
-      </c>
-      <c r="K182" s="7" t="s">
-        <v>390</v>
       </c>
       <c r="L182">
         <v>149800</v>
@@ -9492,7 +9488,7 @@
         <v>13</v>
       </c>
       <c r="C183" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D183" t="s">
         <v>15</v>
@@ -9501,10 +9497,10 @@
         <v>16</v>
       </c>
       <c r="J183" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="K183" s="7" t="s">
         <v>391</v>
-      </c>
-      <c r="K183" s="7" t="s">
-        <v>392</v>
       </c>
       <c r="L183">
         <v>214000</v>
@@ -9521,7 +9517,7 @@
         <v>13</v>
       </c>
       <c r="C184" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D184" t="s">
         <v>15</v>
@@ -9530,10 +9526,10 @@
         <v>16</v>
       </c>
       <c r="J184" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="K184" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="K184" s="7" t="s">
-        <v>394</v>
       </c>
       <c r="L184">
         <v>277986</v>
@@ -9550,7 +9546,7 @@
         <v>13</v>
       </c>
       <c r="C185" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D185" t="s">
         <v>15</v>
@@ -9559,10 +9555,10 @@
         <v>16</v>
       </c>
       <c r="J185" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="K185" s="7" t="s">
         <v>395</v>
-      </c>
-      <c r="K185" s="7" t="s">
-        <v>396</v>
       </c>
       <c r="L185">
         <v>277986</v>
@@ -9579,7 +9575,7 @@
         <v>13</v>
       </c>
       <c r="C186" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D186" t="s">
         <v>15</v>
@@ -9588,10 +9584,10 @@
         <v>16</v>
       </c>
       <c r="J186" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="K186" s="7" t="s">
         <v>397</v>
-      </c>
-      <c r="K186" s="7" t="s">
-        <v>398</v>
       </c>
       <c r="L186">
         <v>187849</v>
@@ -9608,19 +9604,19 @@
         <v>13</v>
       </c>
       <c r="C187" t="s">
+        <v>398</v>
+      </c>
+      <c r="D187" t="s">
+        <v>15</v>
+      </c>
+      <c r="F187" t="s">
+        <v>16</v>
+      </c>
+      <c r="J187" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="D187" t="s">
-        <v>15</v>
-      </c>
-      <c r="F187" t="s">
-        <v>16</v>
-      </c>
-      <c r="J187" s="10" t="s">
+      <c r="K187" s="7" t="s">
         <v>400</v>
-      </c>
-      <c r="K187" s="7" t="s">
-        <v>401</v>
       </c>
       <c r="L187">
         <v>90000</v>
@@ -9637,7 +9633,7 @@
         <v>13</v>
       </c>
       <c r="C188" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D188" t="s">
         <v>15</v>
@@ -9646,10 +9642,10 @@
         <v>16</v>
       </c>
       <c r="J188" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="K188" s="7" t="s">
         <v>402</v>
-      </c>
-      <c r="K188" s="7" t="s">
-        <v>403</v>
       </c>
       <c r="L188">
         <v>90000</v>
@@ -9666,7 +9662,7 @@
         <v>13</v>
       </c>
       <c r="C189" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D189" t="s">
         <v>15</v>
@@ -9675,10 +9671,10 @@
         <v>16</v>
       </c>
       <c r="J189" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="K189" s="7" t="s">
         <v>404</v>
-      </c>
-      <c r="K189" s="7" t="s">
-        <v>405</v>
       </c>
       <c r="L189">
         <v>90000</v>
@@ -9695,7 +9691,7 @@
         <v>13</v>
       </c>
       <c r="C190" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D190" t="s">
         <v>15</v>
@@ -9704,10 +9700,10 @@
         <v>16</v>
       </c>
       <c r="J190" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="K190" s="7" t="s">
         <v>406</v>
-      </c>
-      <c r="K190" s="7" t="s">
-        <v>407</v>
       </c>
       <c r="L190">
         <v>90000</v>
@@ -9724,7 +9720,7 @@
         <v>13</v>
       </c>
       <c r="C191" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D191" t="s">
         <v>15</v>
@@ -9733,10 +9729,10 @@
         <v>16</v>
       </c>
       <c r="J191" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="K191" s="7" t="s">
         <v>408</v>
-      </c>
-      <c r="K191" s="7" t="s">
-        <v>409</v>
       </c>
       <c r="L191">
         <v>276038</v>
@@ -9753,7 +9749,7 @@
         <v>13</v>
       </c>
       <c r="C192" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D192" t="s">
         <v>15</v>
@@ -9762,10 +9758,10 @@
         <v>16</v>
       </c>
       <c r="J192" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="K192" s="7" t="s">
         <v>410</v>
-      </c>
-      <c r="K192" s="7" t="s">
-        <v>411</v>
       </c>
       <c r="L192">
         <v>276038</v>
@@ -9782,7 +9778,7 @@
         <v>13</v>
       </c>
       <c r="C193" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D193" t="s">
         <v>15</v>
@@ -9791,10 +9787,10 @@
         <v>16</v>
       </c>
       <c r="J193" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="K193" s="7" t="s">
         <v>412</v>
-      </c>
-      <c r="K193" s="7" t="s">
-        <v>413</v>
       </c>
       <c r="L193">
         <v>276038</v>
@@ -9811,7 +9807,7 @@
         <v>13</v>
       </c>
       <c r="C194" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D194" t="s">
         <v>15</v>
@@ -9820,10 +9816,10 @@
         <v>16</v>
       </c>
       <c r="J194" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="K194" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="K194" s="7" t="s">
-        <v>415</v>
       </c>
       <c r="L194">
         <v>276038</v>
@@ -9840,7 +9836,7 @@
         <v>13</v>
       </c>
       <c r="C195" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D195" t="s">
         <v>15</v>
@@ -9849,10 +9845,10 @@
         <v>16</v>
       </c>
       <c r="J195" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="K195" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="K195" s="7" t="s">
-        <v>417</v>
       </c>
       <c r="L195">
         <v>276038</v>
@@ -9869,7 +9865,7 @@
         <v>13</v>
       </c>
       <c r="C196" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D196" t="s">
         <v>15</v>
@@ -9878,10 +9874,10 @@
         <v>16</v>
       </c>
       <c r="J196" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="K196" s="7" t="s">
         <v>418</v>
-      </c>
-      <c r="K196" s="7" t="s">
-        <v>419</v>
       </c>
       <c r="L196">
         <v>276038</v>
@@ -9898,7 +9894,7 @@
         <v>13</v>
       </c>
       <c r="C197" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D197" t="s">
         <v>15</v>
@@ -9907,10 +9903,10 @@
         <v>16</v>
       </c>
       <c r="J197" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="K197" s="7" t="s">
         <v>420</v>
-      </c>
-      <c r="K197" s="7" t="s">
-        <v>421</v>
       </c>
       <c r="L197">
         <v>276038</v>
@@ -9927,7 +9923,7 @@
         <v>13</v>
       </c>
       <c r="C198" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D198" t="s">
         <v>15</v>
@@ -9936,10 +9932,10 @@
         <v>16</v>
       </c>
       <c r="J198" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="K198" s="7" t="s">
         <v>422</v>
-      </c>
-      <c r="K198" s="7" t="s">
-        <v>423</v>
       </c>
       <c r="L198">
         <v>276038</v>
@@ -9956,7 +9952,7 @@
         <v>13</v>
       </c>
       <c r="C199" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D199" t="s">
         <v>15</v>
@@ -9965,10 +9961,10 @@
         <v>16</v>
       </c>
       <c r="J199" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="K199" s="7" t="s">
         <v>424</v>
-      </c>
-      <c r="K199" s="7" t="s">
-        <v>425</v>
       </c>
       <c r="L199">
         <v>276038</v>
@@ -9985,7 +9981,7 @@
         <v>13</v>
       </c>
       <c r="C200" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D200" t="s">
         <v>15</v>
@@ -9994,10 +9990,10 @@
         <v>16</v>
       </c>
       <c r="J200" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="K200" s="7" t="s">
         <v>426</v>
-      </c>
-      <c r="K200" s="7" t="s">
-        <v>427</v>
       </c>
       <c r="L200">
         <v>276038</v>
@@ -10014,7 +10010,7 @@
         <v>13</v>
       </c>
       <c r="C201" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D201" t="s">
         <v>15</v>
@@ -10023,10 +10019,10 @@
         <v>16</v>
       </c>
       <c r="J201" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="K201" s="7" t="s">
         <v>428</v>
-      </c>
-      <c r="K201" s="7" t="s">
-        <v>429</v>
       </c>
       <c r="L201">
         <v>276038</v>
@@ -10043,7 +10039,7 @@
         <v>13</v>
       </c>
       <c r="C202" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D202" t="s">
         <v>15</v>
@@ -10052,10 +10048,10 @@
         <v>16</v>
       </c>
       <c r="J202" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="K202" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="K202" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="L202">
         <v>276038</v>
@@ -10072,7 +10068,7 @@
         <v>13</v>
       </c>
       <c r="C203" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D203" t="s">
         <v>15</v>
@@ -10081,10 +10077,10 @@
         <v>16</v>
       </c>
       <c r="J203" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="K203" s="7" t="s">
         <v>432</v>
-      </c>
-      <c r="K203" s="7" t="s">
-        <v>433</v>
       </c>
       <c r="L203">
         <v>276038</v>
@@ -10101,7 +10097,7 @@
         <v>13</v>
       </c>
       <c r="C204" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D204" t="s">
         <v>15</v>
@@ -10110,10 +10106,10 @@
         <v>16</v>
       </c>
       <c r="J204" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="K204" s="7" t="s">
         <v>434</v>
-      </c>
-      <c r="K204" s="7" t="s">
-        <v>435</v>
       </c>
       <c r="L204">
         <v>276038</v>
@@ -10130,7 +10126,7 @@
         <v>13</v>
       </c>
       <c r="C205" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D205" t="s">
         <v>15</v>
@@ -10139,10 +10135,10 @@
         <v>16</v>
       </c>
       <c r="J205" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="K205" s="7" t="s">
         <v>436</v>
-      </c>
-      <c r="K205" s="7" t="s">
-        <v>437</v>
       </c>
       <c r="L205">
         <v>276038</v>
@@ -10159,7 +10155,7 @@
         <v>13</v>
       </c>
       <c r="C206" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D206" t="s">
         <v>15</v>
@@ -10168,10 +10164,10 @@
         <v>16</v>
       </c>
       <c r="J206" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="K206" s="7" t="s">
         <v>438</v>
-      </c>
-      <c r="K206" s="7" t="s">
-        <v>439</v>
       </c>
       <c r="L206">
         <v>276038</v>
@@ -10188,7 +10184,7 @@
         <v>13</v>
       </c>
       <c r="C207" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D207" t="s">
         <v>15</v>
@@ -10197,10 +10193,10 @@
         <v>16</v>
       </c>
       <c r="J207" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="K207" s="7" t="s">
         <v>440</v>
-      </c>
-      <c r="K207" s="7" t="s">
-        <v>441</v>
       </c>
       <c r="L207">
         <v>276038</v>
@@ -10217,7 +10213,7 @@
         <v>13</v>
       </c>
       <c r="C208" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D208" t="s">
         <v>15</v>
@@ -10226,10 +10222,10 @@
         <v>16</v>
       </c>
       <c r="J208" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="K208" s="7" t="s">
         <v>442</v>
-      </c>
-      <c r="K208" s="7" t="s">
-        <v>443</v>
       </c>
       <c r="L208">
         <v>276038</v>
@@ -10246,7 +10242,7 @@
         <v>13</v>
       </c>
       <c r="C209" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D209" t="s">
         <v>15</v>
@@ -10255,10 +10251,10 @@
         <v>16</v>
       </c>
       <c r="J209" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="K209" s="7" t="s">
         <v>444</v>
-      </c>
-      <c r="K209" s="7" t="s">
-        <v>445</v>
       </c>
       <c r="L209">
         <v>276038</v>
@@ -10275,7 +10271,7 @@
         <v>13</v>
       </c>
       <c r="C210" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D210" t="s">
         <v>15</v>
@@ -10284,10 +10280,10 @@
         <v>16</v>
       </c>
       <c r="J210" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="K210" s="7" t="s">
         <v>446</v>
-      </c>
-      <c r="K210" s="7" t="s">
-        <v>447</v>
       </c>
       <c r="L210">
         <v>276038</v>
@@ -10304,7 +10300,7 @@
         <v>13</v>
       </c>
       <c r="C211" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D211" t="s">
         <v>15</v>
@@ -10313,10 +10309,10 @@
         <v>16</v>
       </c>
       <c r="J211" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="K211" s="7" t="s">
         <v>448</v>
-      </c>
-      <c r="K211" s="7" t="s">
-        <v>449</v>
       </c>
       <c r="L211">
         <v>276038</v>
@@ -10333,7 +10329,7 @@
         <v>13</v>
       </c>
       <c r="C212" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D212" t="s">
         <v>15</v>
@@ -10342,10 +10338,10 @@
         <v>16</v>
       </c>
       <c r="J212" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="K212" s="7" t="s">
         <v>450</v>
-      </c>
-      <c r="K212" s="7" t="s">
-        <v>451</v>
       </c>
       <c r="L212">
         <v>276038</v>
@@ -10362,7 +10358,7 @@
         <v>13</v>
       </c>
       <c r="C213" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D213" t="s">
         <v>15</v>
@@ -10371,10 +10367,10 @@
         <v>16</v>
       </c>
       <c r="J213" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="K213" s="7" t="s">
         <v>452</v>
-      </c>
-      <c r="K213" s="7" t="s">
-        <v>453</v>
       </c>
       <c r="L213">
         <v>276038</v>
@@ -10391,7 +10387,7 @@
         <v>13</v>
       </c>
       <c r="C214" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D214" t="s">
         <v>15</v>
@@ -10400,10 +10396,10 @@
         <v>16</v>
       </c>
       <c r="J214" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="K214" s="7" t="s">
         <v>454</v>
-      </c>
-      <c r="K214" s="7" t="s">
-        <v>455</v>
       </c>
       <c r="L214">
         <v>276038</v>
@@ -10420,7 +10416,7 @@
         <v>13</v>
       </c>
       <c r="C215" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D215" t="s">
         <v>15</v>
@@ -10429,10 +10425,10 @@
         <v>16</v>
       </c>
       <c r="J215" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="K215" s="7" t="s">
         <v>456</v>
-      </c>
-      <c r="K215" s="7" t="s">
-        <v>457</v>
       </c>
       <c r="L215">
         <v>276038</v>
@@ -10449,7 +10445,7 @@
         <v>13</v>
       </c>
       <c r="C216" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D216" t="s">
         <v>15</v>
@@ -10458,10 +10454,10 @@
         <v>16</v>
       </c>
       <c r="J216" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="K216" s="7" t="s">
         <v>458</v>
-      </c>
-      <c r="K216" s="7" t="s">
-        <v>459</v>
       </c>
       <c r="L216">
         <v>276038</v>
@@ -10478,7 +10474,7 @@
         <v>13</v>
       </c>
       <c r="C217" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D217" t="s">
         <v>15</v>
@@ -10487,10 +10483,10 @@
         <v>16</v>
       </c>
       <c r="J217" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="K217" s="7" t="s">
         <v>460</v>
-      </c>
-      <c r="K217" s="7" t="s">
-        <v>461</v>
       </c>
       <c r="L217">
         <v>276038</v>
@@ -10507,7 +10503,7 @@
         <v>13</v>
       </c>
       <c r="C218" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D218" t="s">
         <v>15</v>
@@ -10516,10 +10512,10 @@
         <v>16</v>
       </c>
       <c r="J218" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="K218" s="7" t="s">
         <v>462</v>
-      </c>
-      <c r="K218" s="7" t="s">
-        <v>463</v>
       </c>
       <c r="L218">
         <v>276038</v>
@@ -10536,7 +10532,7 @@
         <v>13</v>
       </c>
       <c r="C219" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D219" t="s">
         <v>15</v>
@@ -10545,10 +10541,10 @@
         <v>16</v>
       </c>
       <c r="J219" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="K219" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="K219" s="7" t="s">
-        <v>465</v>
       </c>
       <c r="L219">
         <v>276038</v>
@@ -10565,7 +10561,7 @@
         <v>13</v>
       </c>
       <c r="C220" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D220" t="s">
         <v>15</v>
@@ -10574,10 +10570,10 @@
         <v>16</v>
       </c>
       <c r="J220" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="K220" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="K220" s="7" t="s">
-        <v>467</v>
       </c>
       <c r="L220">
         <v>276038</v>
@@ -10594,7 +10590,7 @@
         <v>13</v>
       </c>
       <c r="C221" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D221" t="s">
         <v>15</v>
@@ -10603,10 +10599,10 @@
         <v>16</v>
       </c>
       <c r="J221" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="K221" s="7" t="s">
         <v>468</v>
-      </c>
-      <c r="K221" s="7" t="s">
-        <v>469</v>
       </c>
       <c r="L221">
         <v>276038</v>
@@ -10623,7 +10619,7 @@
         <v>13</v>
       </c>
       <c r="C222" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D222" t="s">
         <v>15</v>
@@ -10632,10 +10628,10 @@
         <v>16</v>
       </c>
       <c r="J222" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="K222" s="7" t="s">
         <v>470</v>
-      </c>
-      <c r="K222" s="7" t="s">
-        <v>471</v>
       </c>
       <c r="L222">
         <v>276038</v>
@@ -10652,7 +10648,7 @@
         <v>13</v>
       </c>
       <c r="C223" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D223" t="s">
         <v>15</v>
@@ -10661,10 +10657,10 @@
         <v>16</v>
       </c>
       <c r="J223" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="K223" s="7" t="s">
         <v>472</v>
-      </c>
-      <c r="K223" s="7" t="s">
-        <v>473</v>
       </c>
       <c r="L223">
         <v>276038</v>
@@ -10681,7 +10677,7 @@
         <v>13</v>
       </c>
       <c r="C224" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D224" t="s">
         <v>15</v>
@@ -10690,10 +10686,10 @@
         <v>16</v>
       </c>
       <c r="J224" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="K224" s="7" t="s">
         <v>474</v>
-      </c>
-      <c r="K224" s="7" t="s">
-        <v>475</v>
       </c>
       <c r="L224">
         <v>276038</v>
@@ -10710,7 +10706,7 @@
         <v>13</v>
       </c>
       <c r="C225" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D225" t="s">
         <v>15</v>
@@ -10719,10 +10715,10 @@
         <v>16</v>
       </c>
       <c r="J225" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="K225" s="7" t="s">
         <v>476</v>
-      </c>
-      <c r="K225" s="7" t="s">
-        <v>477</v>
       </c>
       <c r="L225">
         <v>276038</v>
@@ -10739,7 +10735,7 @@
         <v>13</v>
       </c>
       <c r="C226" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D226" t="s">
         <v>15</v>
@@ -10748,10 +10744,10 @@
         <v>16</v>
       </c>
       <c r="J226" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="K226" s="7" t="s">
         <v>478</v>
-      </c>
-      <c r="K226" s="7" t="s">
-        <v>479</v>
       </c>
       <c r="L226">
         <v>276038</v>
@@ -10768,7 +10764,7 @@
         <v>13</v>
       </c>
       <c r="C227" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D227" t="s">
         <v>15</v>
@@ -10777,10 +10773,10 @@
         <v>16</v>
       </c>
       <c r="J227" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="K227" s="7" t="s">
         <v>480</v>
-      </c>
-      <c r="K227" s="7" t="s">
-        <v>481</v>
       </c>
       <c r="L227">
         <v>276038</v>
@@ -10797,7 +10793,7 @@
         <v>13</v>
       </c>
       <c r="C228" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D228" t="s">
         <v>15</v>
@@ -10806,10 +10802,10 @@
         <v>16</v>
       </c>
       <c r="J228" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="K228" s="7" t="s">
         <v>482</v>
-      </c>
-      <c r="K228" s="7" t="s">
-        <v>483</v>
       </c>
       <c r="L228">
         <v>276038</v>
@@ -10826,7 +10822,7 @@
         <v>13</v>
       </c>
       <c r="C229" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D229" t="s">
         <v>15</v>
@@ -10835,10 +10831,10 @@
         <v>16</v>
       </c>
       <c r="J229" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="K229" s="7" t="s">
         <v>484</v>
-      </c>
-      <c r="K229" s="7" t="s">
-        <v>485</v>
       </c>
       <c r="L229">
         <v>276038</v>
@@ -10855,7 +10851,7 @@
         <v>13</v>
       </c>
       <c r="C230" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D230" t="s">
         <v>15</v>
@@ -10864,10 +10860,10 @@
         <v>16</v>
       </c>
       <c r="J230" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="K230" s="7" t="s">
         <v>486</v>
-      </c>
-      <c r="K230" s="7" t="s">
-        <v>487</v>
       </c>
       <c r="L230">
         <v>276038</v>
@@ -10884,7 +10880,7 @@
         <v>13</v>
       </c>
       <c r="C231" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D231" t="s">
         <v>15</v>
@@ -10893,10 +10889,10 @@
         <v>16</v>
       </c>
       <c r="J231" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="K231" s="7" t="s">
         <v>488</v>
-      </c>
-      <c r="K231" s="7" t="s">
-        <v>489</v>
       </c>
       <c r="L231">
         <v>276038</v>
@@ -10913,7 +10909,7 @@
         <v>13</v>
       </c>
       <c r="C232" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D232" t="s">
         <v>15</v>
@@ -10922,10 +10918,10 @@
         <v>16</v>
       </c>
       <c r="J232" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="K232" s="7" t="s">
         <v>490</v>
-      </c>
-      <c r="K232" s="7" t="s">
-        <v>491</v>
       </c>
       <c r="L232">
         <v>276038</v>
@@ -10942,7 +10938,7 @@
         <v>13</v>
       </c>
       <c r="C233" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D233" t="s">
         <v>15</v>
@@ -10951,10 +10947,10 @@
         <v>16</v>
       </c>
       <c r="J233" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="K233" s="7" t="s">
         <v>492</v>
-      </c>
-      <c r="K233" s="7" t="s">
-        <v>493</v>
       </c>
       <c r="L233">
         <v>276038</v>
@@ -10971,7 +10967,7 @@
         <v>13</v>
       </c>
       <c r="C234" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D234" t="s">
         <v>15</v>
@@ -10980,10 +10976,10 @@
         <v>16</v>
       </c>
       <c r="J234" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="K234" s="7" t="s">
         <v>494</v>
-      </c>
-      <c r="K234" s="7" t="s">
-        <v>495</v>
       </c>
       <c r="L234">
         <v>276038</v>
@@ -11000,7 +10996,7 @@
         <v>13</v>
       </c>
       <c r="C235" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D235" t="s">
         <v>15</v>
@@ -11009,10 +11005,10 @@
         <v>16</v>
       </c>
       <c r="J235" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="K235" s="7" t="s">
         <v>496</v>
-      </c>
-      <c r="K235" s="7" t="s">
-        <v>497</v>
       </c>
       <c r="L235">
         <v>276038</v>
@@ -11029,7 +11025,7 @@
         <v>13</v>
       </c>
       <c r="C236" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D236" t="s">
         <v>15</v>
@@ -11038,10 +11034,10 @@
         <v>16</v>
       </c>
       <c r="J236" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="K236" s="7" t="s">
         <v>498</v>
-      </c>
-      <c r="K236" s="7" t="s">
-        <v>499</v>
       </c>
       <c r="L236">
         <v>276038</v>
@@ -11058,7 +11054,7 @@
         <v>13</v>
       </c>
       <c r="C237" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D237" t="s">
         <v>15</v>
@@ -11067,10 +11063,10 @@
         <v>16</v>
       </c>
       <c r="J237" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="K237" s="7" t="s">
         <v>500</v>
-      </c>
-      <c r="K237" s="7" t="s">
-        <v>501</v>
       </c>
       <c r="L237">
         <v>276038</v>
@@ -11087,7 +11083,7 @@
         <v>13</v>
       </c>
       <c r="C238" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D238" t="s">
         <v>15</v>
@@ -11096,10 +11092,10 @@
         <v>16</v>
       </c>
       <c r="J238" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="K238" s="7" t="s">
         <v>502</v>
-      </c>
-      <c r="K238" s="7" t="s">
-        <v>503</v>
       </c>
       <c r="L238">
         <v>276038</v>
@@ -11116,7 +11112,7 @@
         <v>13</v>
       </c>
       <c r="C239" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
         <v>15</v>
@@ -11125,10 +11121,10 @@
         <v>16</v>
       </c>
       <c r="J239" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="K239" s="7" t="s">
         <v>504</v>
-      </c>
-      <c r="K239" s="7" t="s">
-        <v>505</v>
       </c>
       <c r="L239">
         <v>276038</v>
@@ -11145,7 +11141,7 @@
         <v>13</v>
       </c>
       <c r="C240" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D240" t="s">
         <v>15</v>
@@ -11154,10 +11150,10 @@
         <v>16</v>
       </c>
       <c r="J240" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="K240" s="7" t="s">
         <v>506</v>
-      </c>
-      <c r="K240" s="7" t="s">
-        <v>507</v>
       </c>
       <c r="L240">
         <v>292600</v>
@@ -11174,7 +11170,7 @@
         <v>13</v>
       </c>
       <c r="C241" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D241" t="s">
         <v>15</v>
@@ -11183,10 +11179,10 @@
         <v>16</v>
       </c>
       <c r="J241" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="K241" s="7" t="s">
         <v>508</v>
-      </c>
-      <c r="K241" s="7" t="s">
-        <v>509</v>
       </c>
       <c r="L241">
         <v>292600</v>
@@ -11203,7 +11199,7 @@
         <v>13</v>
       </c>
       <c r="C242" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D242" t="s">
         <v>15</v>
@@ -11212,10 +11208,10 @@
         <v>16</v>
       </c>
       <c r="J242" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="K242" s="7" t="s">
         <v>510</v>
-      </c>
-      <c r="K242" s="7" t="s">
-        <v>511</v>
       </c>
       <c r="L242">
         <v>292600</v>
@@ -11232,7 +11228,7 @@
         <v>13</v>
       </c>
       <c r="C243" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D243" t="s">
         <v>15</v>
@@ -11241,10 +11237,10 @@
         <v>16</v>
       </c>
       <c r="J243" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="K243" s="7" t="s">
         <v>512</v>
-      </c>
-      <c r="K243" s="7" t="s">
-        <v>513</v>
       </c>
       <c r="L243">
         <v>292600</v>
@@ -11261,7 +11257,7 @@
         <v>13</v>
       </c>
       <c r="C244" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D244" t="s">
         <v>15</v>
@@ -11270,10 +11266,10 @@
         <v>16</v>
       </c>
       <c r="J244" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="K244" s="7" t="s">
         <v>514</v>
-      </c>
-      <c r="K244" s="7" t="s">
-        <v>515</v>
       </c>
       <c r="L244">
         <v>292600</v>
@@ -11290,7 +11286,7 @@
         <v>13</v>
       </c>
       <c r="C245" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D245" t="s">
         <v>15</v>
@@ -11299,10 +11295,10 @@
         <v>16</v>
       </c>
       <c r="J245" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="K245" s="7" t="s">
         <v>516</v>
-      </c>
-      <c r="K245" s="7" t="s">
-        <v>517</v>
       </c>
       <c r="L245">
         <v>90000</v>
@@ -11319,7 +11315,7 @@
         <v>13</v>
       </c>
       <c r="C246" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D246" t="s">
         <v>15</v>
@@ -11328,10 +11324,10 @@
         <v>16</v>
       </c>
       <c r="J246" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="K246" s="7" t="s">
         <v>518</v>
-      </c>
-      <c r="K246" s="7" t="s">
-        <v>519</v>
       </c>
       <c r="L246">
         <v>45000</v>
@@ -11348,7 +11344,7 @@
         <v>13</v>
       </c>
       <c r="C247" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D247" t="s">
         <v>15</v>
@@ -11357,10 +11353,10 @@
         <v>16</v>
       </c>
       <c r="J247" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="K247" s="7" t="s">
         <v>520</v>
-      </c>
-      <c r="K247" s="7" t="s">
-        <v>521</v>
       </c>
       <c r="L247">
         <v>90000</v>
@@ -11377,7 +11373,7 @@
         <v>13</v>
       </c>
       <c r="C248" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D248" t="s">
         <v>15</v>
@@ -11386,10 +11382,10 @@
         <v>16</v>
       </c>
       <c r="J248" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="K248" s="7" t="s">
         <v>522</v>
-      </c>
-      <c r="K248" s="7" t="s">
-        <v>523</v>
       </c>
       <c r="L248">
         <v>90000</v>
@@ -11406,7 +11402,7 @@
         <v>13</v>
       </c>
       <c r="C249" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D249" t="s">
         <v>15</v>
@@ -11415,10 +11411,10 @@
         <v>16</v>
       </c>
       <c r="J249" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="K249" s="7" t="s">
         <v>524</v>
-      </c>
-      <c r="K249" s="7" t="s">
-        <v>525</v>
       </c>
       <c r="L249">
         <v>90000</v>
@@ -11435,7 +11431,7 @@
         <v>13</v>
       </c>
       <c r="C250" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D250" t="s">
         <v>15</v>
@@ -11444,10 +11440,10 @@
         <v>16</v>
       </c>
       <c r="J250" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="K250" s="7" t="s">
         <v>526</v>
-      </c>
-      <c r="K250" s="7" t="s">
-        <v>527</v>
       </c>
       <c r="L250">
         <v>90000</v>
@@ -11464,7 +11460,7 @@
         <v>13</v>
       </c>
       <c r="C251" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D251" t="s">
         <v>15</v>
@@ -11473,10 +11469,10 @@
         <v>16</v>
       </c>
       <c r="J251" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="K251" s="7" t="s">
         <v>528</v>
-      </c>
-      <c r="K251" s="7" t="s">
-        <v>529</v>
       </c>
       <c r="L251">
         <v>90000</v>
@@ -11493,7 +11489,7 @@
         <v>13</v>
       </c>
       <c r="C252" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D252" t="s">
         <v>15</v>
@@ -11502,10 +11498,10 @@
         <v>16</v>
       </c>
       <c r="J252" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="K252" s="7" t="s">
         <v>530</v>
-      </c>
-      <c r="K252" s="7" t="s">
-        <v>531</v>
       </c>
       <c r="L252">
         <v>90000</v>
@@ -11522,7 +11518,7 @@
         <v>13</v>
       </c>
       <c r="C253" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D253" t="s">
         <v>15</v>
@@ -11531,10 +11527,10 @@
         <v>16</v>
       </c>
       <c r="J253" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="K253" s="7" t="s">
         <v>532</v>
-      </c>
-      <c r="K253" s="7" t="s">
-        <v>533</v>
       </c>
       <c r="L253">
         <v>125000</v>
@@ -11551,7 +11547,7 @@
         <v>13</v>
       </c>
       <c r="C254" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D254" t="s">
         <v>15</v>
@@ -11560,10 +11556,10 @@
         <v>16</v>
       </c>
       <c r="J254" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="K254" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="K254" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="L254">
         <v>108900</v>
@@ -11580,7 +11576,7 @@
         <v>13</v>
       </c>
       <c r="C255" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D255" t="s">
         <v>15</v>
@@ -11589,10 +11585,10 @@
         <v>16</v>
       </c>
       <c r="J255" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="K255" s="7" t="s">
         <v>536</v>
-      </c>
-      <c r="K255" s="7" t="s">
-        <v>537</v>
       </c>
       <c r="L255">
         <v>108000</v>
@@ -11609,7 +11605,7 @@
         <v>13</v>
       </c>
       <c r="C256" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D256" t="s">
         <v>15</v>
@@ -11618,10 +11614,10 @@
         <v>16</v>
       </c>
       <c r="J256" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="K256" s="7" t="s">
         <v>538</v>
-      </c>
-      <c r="K256" s="7" t="s">
-        <v>539</v>
       </c>
       <c r="L256">
         <v>26400</v>
@@ -11638,7 +11634,7 @@
         <v>13</v>
       </c>
       <c r="C257" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D257" t="s">
         <v>15</v>
@@ -11647,16 +11643,16 @@
         <v>16</v>
       </c>
       <c r="J257" s="21" t="s">
+        <v>539</v>
+      </c>
+      <c r="K257" s="7" t="s">
         <v>540</v>
-      </c>
-      <c r="K257" s="7" t="s">
-        <v>541</v>
       </c>
       <c r="L257">
         <v>93925</v>
       </c>
       <c r="M257" s="16" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="258" spans="1:13">
@@ -11667,7 +11663,7 @@
         <v>13</v>
       </c>
       <c r="C258" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D258" t="s">
         <v>15</v>
@@ -11676,10 +11672,10 @@
         <v>16</v>
       </c>
       <c r="J258" s="22" t="s">
+        <v>542</v>
+      </c>
+      <c r="K258" s="7" t="s">
         <v>543</v>
-      </c>
-      <c r="K258" s="7" t="s">
-        <v>544</v>
       </c>
       <c r="L258">
         <v>2391235</v>
@@ -11696,7 +11692,7 @@
         <v>13</v>
       </c>
       <c r="C259" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D259" t="s">
         <v>15</v>
@@ -11705,10 +11701,10 @@
         <v>16</v>
       </c>
       <c r="J259" s="22" t="s">
+        <v>544</v>
+      </c>
+      <c r="K259" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="K259" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="L259">
         <v>100000</v>
@@ -11725,7 +11721,7 @@
         <v>13</v>
       </c>
       <c r="C260" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D260" t="s">
         <v>15</v>
@@ -11734,10 +11730,10 @@
         <v>16</v>
       </c>
       <c r="J260" s="22" t="s">
+        <v>546</v>
+      </c>
+      <c r="K260" s="7" t="s">
         <v>547</v>
-      </c>
-      <c r="K260" s="7" t="s">
-        <v>548</v>
       </c>
       <c r="L260">
         <v>150000</v>
@@ -11754,7 +11750,7 @@
         <v>13</v>
       </c>
       <c r="C261" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D261" t="s">
         <v>15</v>
@@ -11763,10 +11759,10 @@
         <v>16</v>
       </c>
       <c r="J261" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="K261" s="7" t="s">
         <v>549</v>
-      </c>
-      <c r="K261" s="7" t="s">
-        <v>550</v>
       </c>
       <c r="L261">
         <v>300000</v>
@@ -11783,7 +11779,7 @@
         <v>13</v>
       </c>
       <c r="C262" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D262" t="s">
         <v>15</v>
@@ -11792,10 +11788,10 @@
         <v>16</v>
       </c>
       <c r="J262" s="22" t="s">
+        <v>550</v>
+      </c>
+      <c r="K262" s="7" t="s">
         <v>551</v>
-      </c>
-      <c r="K262" s="7" t="s">
-        <v>552</v>
       </c>
       <c r="L262">
         <v>3290000</v>
@@ -11812,7 +11808,7 @@
         <v>13</v>
       </c>
       <c r="C263" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D263" t="s">
         <v>15</v>
@@ -11821,10 +11817,10 @@
         <v>16</v>
       </c>
       <c r="J263" s="22" t="s">
+        <v>552</v>
+      </c>
+      <c r="K263" s="7" t="s">
         <v>553</v>
-      </c>
-      <c r="K263" s="7" t="s">
-        <v>554</v>
       </c>
       <c r="L263">
         <v>300000</v>
@@ -11841,7 +11837,7 @@
         <v>13</v>
       </c>
       <c r="C264" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D264" t="s">
         <v>15</v>
@@ -11850,10 +11846,10 @@
         <v>16</v>
       </c>
       <c r="J264" s="22" t="s">
+        <v>554</v>
+      </c>
+      <c r="K264" s="7" t="s">
         <v>555</v>
-      </c>
-      <c r="K264" s="7" t="s">
-        <v>556</v>
       </c>
       <c r="L264">
         <v>300000</v>
@@ -11870,7 +11866,7 @@
         <v>13</v>
       </c>
       <c r="C265" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D265" t="s">
         <v>15</v>
@@ -11879,10 +11875,10 @@
         <v>16</v>
       </c>
       <c r="J265" s="22" t="s">
+        <v>556</v>
+      </c>
+      <c r="K265" s="7" t="s">
         <v>557</v>
-      </c>
-      <c r="K265" s="7" t="s">
-        <v>558</v>
       </c>
       <c r="L265">
         <v>846000</v>
@@ -11899,7 +11895,7 @@
         <v>13</v>
       </c>
       <c r="C266" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D266" t="s">
         <v>15</v>
@@ -11908,10 +11904,10 @@
         <v>16</v>
       </c>
       <c r="J266" s="22" t="s">
+        <v>558</v>
+      </c>
+      <c r="K266" s="7" t="s">
         <v>559</v>
-      </c>
-      <c r="K266" s="7" t="s">
-        <v>560</v>
       </c>
       <c r="L266">
         <v>300000</v>
@@ -11928,7 +11924,7 @@
         <v>13</v>
       </c>
       <c r="C267" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D267" t="s">
         <v>15</v>
@@ -11937,10 +11933,10 @@
         <v>16</v>
       </c>
       <c r="J267" s="22" t="s">
+        <v>560</v>
+      </c>
+      <c r="K267" s="7" t="s">
         <v>561</v>
-      </c>
-      <c r="K267" s="7" t="s">
-        <v>562</v>
       </c>
       <c r="L267">
         <v>150000</v>
@@ -11957,7 +11953,7 @@
         <v>13</v>
       </c>
       <c r="C268" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D268" t="s">
         <v>15</v>
@@ -11966,10 +11962,10 @@
         <v>16</v>
       </c>
       <c r="J268" s="22" t="s">
+        <v>562</v>
+      </c>
+      <c r="K268" s="7" t="s">
         <v>563</v>
-      </c>
-      <c r="K268" s="7" t="s">
-        <v>564</v>
       </c>
       <c r="L268">
         <v>150000</v>
@@ -11986,7 +11982,7 @@
         <v>13</v>
       </c>
       <c r="C269" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D269" t="s">
         <v>15</v>
@@ -11995,10 +11991,10 @@
         <v>16</v>
       </c>
       <c r="J269" s="22" t="s">
+        <v>564</v>
+      </c>
+      <c r="K269" s="7" t="s">
         <v>565</v>
-      </c>
-      <c r="K269" s="7" t="s">
-        <v>566</v>
       </c>
       <c r="L269">
         <v>300000</v>
@@ -12015,7 +12011,7 @@
         <v>13</v>
       </c>
       <c r="C270" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D270" t="s">
         <v>15</v>
@@ -12024,10 +12020,10 @@
         <v>16</v>
       </c>
       <c r="J270" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="K270" s="7" t="s">
         <v>567</v>
-      </c>
-      <c r="K270" s="7" t="s">
-        <v>568</v>
       </c>
       <c r="L270">
         <v>150000</v>
@@ -12044,7 +12040,7 @@
         <v>13</v>
       </c>
       <c r="C271" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D271" t="s">
         <v>15</v>
@@ -12053,10 +12049,10 @@
         <v>16</v>
       </c>
       <c r="J271" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="K271" s="7" t="s">
         <v>569</v>
-      </c>
-      <c r="K271" s="7" t="s">
-        <v>570</v>
       </c>
       <c r="L271">
         <v>300000</v>
@@ -12073,7 +12069,7 @@
         <v>13</v>
       </c>
       <c r="C272" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D272" t="s">
         <v>15</v>
@@ -12082,10 +12078,10 @@
         <v>16</v>
       </c>
       <c r="J272" s="22" t="s">
+        <v>570</v>
+      </c>
+      <c r="K272" s="7" t="s">
         <v>571</v>
-      </c>
-      <c r="K272" s="7" t="s">
-        <v>572</v>
       </c>
       <c r="L272">
         <v>486000</v>
@@ -12102,7 +12098,7 @@
         <v>13</v>
       </c>
       <c r="C273" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D273" t="s">
         <v>15</v>
@@ -12111,10 +12107,10 @@
         <v>16</v>
       </c>
       <c r="J273" s="22" t="s">
+        <v>572</v>
+      </c>
+      <c r="K273" s="7" t="s">
         <v>573</v>
-      </c>
-      <c r="K273" s="7" t="s">
-        <v>574</v>
       </c>
       <c r="L273">
         <v>300000</v>
@@ -12131,7 +12127,7 @@
         <v>13</v>
       </c>
       <c r="C274" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D274" t="s">
         <v>15</v>
@@ -12140,10 +12136,10 @@
         <v>16</v>
       </c>
       <c r="J274" s="22" t="s">
+        <v>574</v>
+      </c>
+      <c r="K274" s="7" t="s">
         <v>575</v>
-      </c>
-      <c r="K274" s="7" t="s">
-        <v>576</v>
       </c>
       <c r="L274">
         <v>300000</v>
@@ -12160,7 +12156,7 @@
         <v>13</v>
       </c>
       <c r="C275" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D275" t="s">
         <v>15</v>
@@ -12169,10 +12165,10 @@
         <v>16</v>
       </c>
       <c r="J275" s="22" t="s">
+        <v>576</v>
+      </c>
+      <c r="K275" s="7" t="s">
         <v>577</v>
-      </c>
-      <c r="K275" s="7" t="s">
-        <v>578</v>
       </c>
       <c r="L275">
         <v>100000</v>
@@ -12189,7 +12185,7 @@
         <v>13</v>
       </c>
       <c r="C276" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D276" t="s">
         <v>15</v>
@@ -12198,10 +12194,10 @@
         <v>16</v>
       </c>
       <c r="J276" s="22" t="s">
+        <v>578</v>
+      </c>
+      <c r="K276" s="7" t="s">
         <v>579</v>
-      </c>
-      <c r="K276" s="7" t="s">
-        <v>580</v>
       </c>
       <c r="L276">
         <v>300000</v>
@@ -12218,7 +12214,7 @@
         <v>13</v>
       </c>
       <c r="C277" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D277" t="s">
         <v>15</v>
@@ -12227,10 +12223,10 @@
         <v>16</v>
       </c>
       <c r="J277" s="22" t="s">
+        <v>580</v>
+      </c>
+      <c r="K277" s="7" t="s">
         <v>581</v>
-      </c>
-      <c r="K277" s="7" t="s">
-        <v>582</v>
       </c>
       <c r="L277">
         <v>150000</v>
@@ -12247,7 +12243,7 @@
         <v>13</v>
       </c>
       <c r="C278" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D278" t="s">
         <v>15</v>
@@ -12256,10 +12252,10 @@
         <v>16</v>
       </c>
       <c r="J278" s="22" t="s">
+        <v>582</v>
+      </c>
+      <c r="K278" s="7" t="s">
         <v>583</v>
-      </c>
-      <c r="K278" s="7" t="s">
-        <v>584</v>
       </c>
       <c r="L278">
         <v>150000</v>
@@ -12276,7 +12272,7 @@
         <v>13</v>
       </c>
       <c r="C279" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D279" t="s">
         <v>15</v>
@@ -12285,10 +12281,10 @@
         <v>16</v>
       </c>
       <c r="J279" s="22" t="s">
+        <v>584</v>
+      </c>
+      <c r="K279" s="7" t="s">
         <v>585</v>
-      </c>
-      <c r="K279" s="7" t="s">
-        <v>586</v>
       </c>
       <c r="L279">
         <v>150000</v>
@@ -12305,7 +12301,7 @@
         <v>13</v>
       </c>
       <c r="C280" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D280" t="s">
         <v>15</v>
@@ -12314,10 +12310,10 @@
         <v>16</v>
       </c>
       <c r="J280" s="22" t="s">
+        <v>586</v>
+      </c>
+      <c r="K280" s="7" t="s">
         <v>587</v>
-      </c>
-      <c r="K280" s="7" t="s">
-        <v>588</v>
       </c>
       <c r="L280">
         <v>150000</v>
@@ -12334,7 +12330,7 @@
         <v>13</v>
       </c>
       <c r="C281" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D281" t="s">
         <v>15</v>
@@ -12343,10 +12339,10 @@
         <v>16</v>
       </c>
       <c r="J281" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="K281" s="7" t="s">
         <v>589</v>
-      </c>
-      <c r="K281" s="7" t="s">
-        <v>590</v>
       </c>
       <c r="L281">
         <v>97213</v>
@@ -12363,7 +12359,7 @@
         <v>13</v>
       </c>
       <c r="C282" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D282" t="s">
         <v>15</v>
@@ -12372,10 +12368,10 @@
         <v>16</v>
       </c>
       <c r="J282" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="K282" s="7" t="s">
         <v>591</v>
-      </c>
-      <c r="K282" s="7" t="s">
-        <v>592</v>
       </c>
       <c r="L282">
         <v>478487</v>
@@ -12392,7 +12388,7 @@
         <v>13</v>
       </c>
       <c r="C283" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D283" t="s">
         <v>15</v>
@@ -12401,10 +12397,10 @@
         <v>16</v>
       </c>
       <c r="J283" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="K283" s="7" t="s">
         <v>593</v>
-      </c>
-      <c r="K283" s="7" t="s">
-        <v>594</v>
       </c>
       <c r="L283">
         <v>194425</v>
@@ -12421,7 +12417,7 @@
         <v>13</v>
       </c>
       <c r="C284" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D284" t="s">
         <v>15</v>
@@ -12430,10 +12426,10 @@
         <v>16</v>
       </c>
       <c r="J284" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="K284" s="7" t="s">
         <v>595</v>
-      </c>
-      <c r="K284" s="7" t="s">
-        <v>596</v>
       </c>
       <c r="L284">
         <v>130000</v>
@@ -12450,7 +12446,7 @@
         <v>13</v>
       </c>
       <c r="C285" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D285" t="s">
         <v>15</v>
@@ -12459,10 +12455,10 @@
         <v>16</v>
       </c>
       <c r="J285" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="K285" s="7" t="s">
         <v>597</v>
-      </c>
-      <c r="K285" s="7" t="s">
-        <v>598</v>
       </c>
       <c r="L285">
         <v>45000</v>
@@ -12479,7 +12475,7 @@
         <v>13</v>
       </c>
       <c r="C286" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D286" t="s">
         <v>15</v>
@@ -12488,10 +12484,10 @@
         <v>16</v>
       </c>
       <c r="J286" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="K286" s="7" t="s">
         <v>599</v>
-      </c>
-      <c r="K286" s="7" t="s">
-        <v>600</v>
       </c>
       <c r="L286">
         <v>130000</v>
@@ -12508,7 +12504,7 @@
         <v>13</v>
       </c>
       <c r="C287" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D287" t="s">
         <v>15</v>
@@ -12517,10 +12513,10 @@
         <v>16</v>
       </c>
       <c r="J287" s="20" t="s">
+        <v>600</v>
+      </c>
+      <c r="K287" s="7" t="s">
         <v>601</v>
-      </c>
-      <c r="K287" s="7" t="s">
-        <v>602</v>
       </c>
       <c r="L287">
         <v>45000</v>
@@ -12537,7 +12533,7 @@
         <v>13</v>
       </c>
       <c r="C288" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D288" t="s">
         <v>15</v>
@@ -12546,10 +12542,10 @@
         <v>16</v>
       </c>
       <c r="J288" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="K288" s="7" t="s">
         <v>603</v>
-      </c>
-      <c r="K288" s="7" t="s">
-        <v>604</v>
       </c>
       <c r="L288">
         <v>45000</v>
@@ -12566,7 +12562,7 @@
         <v>13</v>
       </c>
       <c r="C289" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D289" t="s">
         <v>15</v>
@@ -12575,10 +12571,10 @@
         <v>16</v>
       </c>
       <c r="J289" s="20" t="s">
+        <v>604</v>
+      </c>
+      <c r="K289" s="7" t="s">
         <v>605</v>
-      </c>
-      <c r="K289" s="7" t="s">
-        <v>606</v>
       </c>
       <c r="L289">
         <v>45000</v>
@@ -12595,7 +12591,7 @@
         <v>13</v>
       </c>
       <c r="C290" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D290" t="s">
         <v>15</v>
@@ -12604,10 +12600,10 @@
         <v>16</v>
       </c>
       <c r="J290" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="K290" s="7" t="s">
         <v>607</v>
-      </c>
-      <c r="K290" s="7" t="s">
-        <v>608</v>
       </c>
       <c r="L290">
         <v>45000</v>
@@ -12624,7 +12620,7 @@
         <v>13</v>
       </c>
       <c r="C291" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D291" t="s">
         <v>15</v>
@@ -12633,10 +12629,10 @@
         <v>16</v>
       </c>
       <c r="J291" s="20" t="s">
+        <v>608</v>
+      </c>
+      <c r="K291" s="7" t="s">
         <v>609</v>
-      </c>
-      <c r="K291" s="7" t="s">
-        <v>610</v>
       </c>
       <c r="L291">
         <v>45000</v>
@@ -12653,7 +12649,7 @@
         <v>13</v>
       </c>
       <c r="C292" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D292" t="s">
         <v>15</v>
@@ -12662,10 +12658,10 @@
         <v>16</v>
       </c>
       <c r="J292" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="K292" s="7" t="s">
         <v>611</v>
-      </c>
-      <c r="K292" s="7" t="s">
-        <v>612</v>
       </c>
       <c r="L292">
         <v>45000</v>
@@ -12682,7 +12678,7 @@
         <v>13</v>
       </c>
       <c r="C293" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D293" t="s">
         <v>15</v>
@@ -12691,10 +12687,10 @@
         <v>16</v>
       </c>
       <c r="J293" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="K293" s="7" t="s">
         <v>613</v>
-      </c>
-      <c r="K293" s="7" t="s">
-        <v>614</v>
       </c>
       <c r="L293">
         <v>45000</v>
@@ -12711,7 +12707,7 @@
         <v>13</v>
       </c>
       <c r="C294" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D294" t="s">
         <v>15</v>
@@ -12720,10 +12716,10 @@
         <v>16</v>
       </c>
       <c r="J294" s="20" t="s">
+        <v>614</v>
+      </c>
+      <c r="K294" s="7" t="s">
         <v>615</v>
-      </c>
-      <c r="K294" s="7" t="s">
-        <v>616</v>
       </c>
       <c r="L294">
         <v>45000</v>
@@ -12740,7 +12736,7 @@
         <v>13</v>
       </c>
       <c r="C295" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D295" t="s">
         <v>15</v>
@@ -12749,10 +12745,10 @@
         <v>16</v>
       </c>
       <c r="J295" s="20" t="s">
+        <v>616</v>
+      </c>
+      <c r="K295" s="7" t="s">
         <v>617</v>
-      </c>
-      <c r="K295" s="7" t="s">
-        <v>618</v>
       </c>
       <c r="L295">
         <v>45000</v>
@@ -12769,7 +12765,7 @@
         <v>13</v>
       </c>
       <c r="C296" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D296" t="s">
         <v>15</v>
@@ -12778,10 +12774,10 @@
         <v>16</v>
       </c>
       <c r="J296" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="K296" s="7" t="s">
         <v>619</v>
-      </c>
-      <c r="K296" s="7" t="s">
-        <v>620</v>
       </c>
       <c r="L296">
         <v>45000</v>
@@ -12798,7 +12794,7 @@
         <v>13</v>
       </c>
       <c r="C297" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D297" t="s">
         <v>15</v>
@@ -12807,10 +12803,10 @@
         <v>16</v>
       </c>
       <c r="J297" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="K297" s="7" t="s">
         <v>621</v>
-      </c>
-      <c r="K297" s="7" t="s">
-        <v>622</v>
       </c>
       <c r="L297">
         <v>130000</v>
@@ -12827,7 +12823,7 @@
         <v>13</v>
       </c>
       <c r="C298" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D298" t="s">
         <v>15</v>
@@ -12836,10 +12832,10 @@
         <v>16</v>
       </c>
       <c r="J298" s="20" t="s">
+        <v>622</v>
+      </c>
+      <c r="K298" s="7" t="s">
         <v>623</v>
-      </c>
-      <c r="K298" s="7" t="s">
-        <v>624</v>
       </c>
       <c r="L298">
         <v>45000</v>
@@ -12856,7 +12852,7 @@
         <v>13</v>
       </c>
       <c r="C299" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D299" t="s">
         <v>15</v>
@@ -12865,10 +12861,10 @@
         <v>16</v>
       </c>
       <c r="J299" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="K299" s="7" t="s">
         <v>625</v>
-      </c>
-      <c r="K299" s="7" t="s">
-        <v>626</v>
       </c>
       <c r="L299">
         <v>45000</v>
@@ -12885,7 +12881,7 @@
         <v>13</v>
       </c>
       <c r="C300" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D300" t="s">
         <v>15</v>
@@ -12894,10 +12890,10 @@
         <v>16</v>
       </c>
       <c r="J300" s="20" t="s">
+        <v>626</v>
+      </c>
+      <c r="K300" s="7" t="s">
         <v>627</v>
-      </c>
-      <c r="K300" s="7" t="s">
-        <v>628</v>
       </c>
       <c r="L300">
         <v>45000</v>
@@ -12914,7 +12910,7 @@
         <v>13</v>
       </c>
       <c r="C301" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D301" t="s">
         <v>15</v>
@@ -12923,10 +12919,10 @@
         <v>16</v>
       </c>
       <c r="J301" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="K301" s="7" t="s">
         <v>629</v>
-      </c>
-      <c r="K301" s="7" t="s">
-        <v>630</v>
       </c>
       <c r="L301">
         <v>45000</v>
@@ -12943,7 +12939,7 @@
         <v>13</v>
       </c>
       <c r="C302" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D302" t="s">
         <v>15</v>
@@ -12952,10 +12948,10 @@
         <v>16</v>
       </c>
       <c r="J302" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="K302" s="7" t="s">
         <v>631</v>
-      </c>
-      <c r="K302" s="7" t="s">
-        <v>632</v>
       </c>
       <c r="L302">
         <v>45000</v>
@@ -12972,7 +12968,7 @@
         <v>13</v>
       </c>
       <c r="C303" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D303" t="s">
         <v>15</v>
@@ -12981,10 +12977,10 @@
         <v>16</v>
       </c>
       <c r="J303" s="20" t="s">
+        <v>632</v>
+      </c>
+      <c r="K303" s="7" t="s">
         <v>633</v>
-      </c>
-      <c r="K303" s="7" t="s">
-        <v>634</v>
       </c>
       <c r="L303">
         <v>45000</v>
@@ -13001,7 +12997,7 @@
         <v>13</v>
       </c>
       <c r="C304" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D304" t="s">
         <v>15</v>
@@ -13010,10 +13006,10 @@
         <v>16</v>
       </c>
       <c r="J304" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="K304" s="7" t="s">
         <v>635</v>
-      </c>
-      <c r="K304" s="7" t="s">
-        <v>636</v>
       </c>
       <c r="L304">
         <v>130000</v>
@@ -13030,7 +13026,7 @@
         <v>13</v>
       </c>
       <c r="C305" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D305" t="s">
         <v>15</v>
@@ -13039,10 +13035,10 @@
         <v>16</v>
       </c>
       <c r="J305" s="20" t="s">
+        <v>636</v>
+      </c>
+      <c r="K305" s="7" t="s">
         <v>637</v>
-      </c>
-      <c r="K305" s="7" t="s">
-        <v>638</v>
       </c>
       <c r="L305">
         <v>45000</v>
@@ -13059,7 +13055,7 @@
         <v>13</v>
       </c>
       <c r="C306" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D306" t="s">
         <v>15</v>
@@ -13068,10 +13064,10 @@
         <v>16</v>
       </c>
       <c r="J306" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="K306" s="7" t="s">
         <v>639</v>
-      </c>
-      <c r="K306" s="7" t="s">
-        <v>640</v>
       </c>
       <c r="L306">
         <v>45000</v>
@@ -13088,7 +13084,7 @@
         <v>13</v>
       </c>
       <c r="C307" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D307" t="s">
         <v>15</v>
@@ -13097,10 +13093,10 @@
         <v>16</v>
       </c>
       <c r="J307" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="K307" s="7" t="s">
         <v>641</v>
-      </c>
-      <c r="K307" s="7" t="s">
-        <v>642</v>
       </c>
       <c r="L307">
         <v>45000</v>
@@ -13117,7 +13113,7 @@
         <v>13</v>
       </c>
       <c r="C308" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D308" t="s">
         <v>15</v>
@@ -13126,10 +13122,10 @@
         <v>16</v>
       </c>
       <c r="J308" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="K308" s="7" t="s">
         <v>643</v>
-      </c>
-      <c r="K308" s="7" t="s">
-        <v>644</v>
       </c>
       <c r="L308">
         <v>45000</v>
@@ -13146,7 +13142,7 @@
         <v>13</v>
       </c>
       <c r="C309" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D309" t="s">
         <v>15</v>
@@ -13155,10 +13151,10 @@
         <v>16</v>
       </c>
       <c r="J309" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K309" s="7" t="s">
         <v>645</v>
-      </c>
-      <c r="K309" s="7" t="s">
-        <v>646</v>
       </c>
       <c r="L309">
         <v>45000</v>
@@ -13175,7 +13171,7 @@
         <v>13</v>
       </c>
       <c r="C310" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D310" t="s">
         <v>15</v>
@@ -13184,10 +13180,10 @@
         <v>16</v>
       </c>
       <c r="J310" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="K310" s="7" t="s">
         <v>647</v>
-      </c>
-      <c r="K310" s="7" t="s">
-        <v>648</v>
       </c>
       <c r="L310">
         <v>130000</v>
@@ -13204,7 +13200,7 @@
         <v>13</v>
       </c>
       <c r="C311" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D311" t="s">
         <v>15</v>
@@ -13213,10 +13209,10 @@
         <v>16</v>
       </c>
       <c r="J311" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="K311" s="7" t="s">
         <v>649</v>
-      </c>
-      <c r="K311" s="7" t="s">
-        <v>650</v>
       </c>
       <c r="L311">
         <v>520000</v>
@@ -13233,7 +13229,7 @@
         <v>13</v>
       </c>
       <c r="C312" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D312" t="s">
         <v>15</v>
@@ -13242,10 +13238,10 @@
         <v>16</v>
       </c>
       <c r="J312" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="K312" s="7" t="s">
         <v>651</v>
-      </c>
-      <c r="K312" s="7" t="s">
-        <v>652</v>
       </c>
       <c r="L312">
         <v>214000</v>
@@ -13262,7 +13258,7 @@
         <v>13</v>
       </c>
       <c r="C313" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D313" t="s">
         <v>15</v>
@@ -13271,10 +13267,10 @@
         <v>16</v>
       </c>
       <c r="J313" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="K313" s="7" t="s">
         <v>653</v>
-      </c>
-      <c r="K313" s="7" t="s">
-        <v>654</v>
       </c>
       <c r="L313">
         <v>214000</v>
@@ -13291,7 +13287,7 @@
         <v>13</v>
       </c>
       <c r="C314" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D314" t="s">
         <v>15</v>
@@ -13300,10 +13296,10 @@
         <v>16</v>
       </c>
       <c r="J314" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="K314" s="7" t="s">
         <v>655</v>
-      </c>
-      <c r="K314" s="7" t="s">
-        <v>656</v>
       </c>
       <c r="L314">
         <v>214000</v>
@@ -13320,7 +13316,7 @@
         <v>13</v>
       </c>
       <c r="C315" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D315" t="s">
         <v>15</v>
@@ -13329,10 +13325,10 @@
         <v>16</v>
       </c>
       <c r="J315" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="K315" s="7" t="s">
         <v>657</v>
-      </c>
-      <c r="K315" s="7" t="s">
-        <v>658</v>
       </c>
       <c r="L315">
         <v>443000</v>
@@ -13349,7 +13345,7 @@
         <v>13</v>
       </c>
       <c r="C316" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D316" t="s">
         <v>15</v>
@@ -13358,10 +13354,10 @@
         <v>16</v>
       </c>
       <c r="J316" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="K316" s="7" t="s">
         <v>659</v>
-      </c>
-      <c r="K316" s="7" t="s">
-        <v>660</v>
       </c>
       <c r="L316">
         <v>31000</v>
@@ -13378,7 +13374,7 @@
         <v>13</v>
       </c>
       <c r="C317" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D317" t="s">
         <v>15</v>
@@ -13387,10 +13383,10 @@
         <v>16</v>
       </c>
       <c r="J317" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="K317" s="7" t="s">
         <v>661</v>
-      </c>
-      <c r="K317" s="7" t="s">
-        <v>662</v>
       </c>
       <c r="L317">
         <v>31000</v>
@@ -13407,7 +13403,7 @@
         <v>13</v>
       </c>
       <c r="C318" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D318" t="s">
         <v>15</v>
@@ -13416,10 +13412,10 @@
         <v>16</v>
       </c>
       <c r="J318" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="K318" s="7" t="s">
         <v>663</v>
-      </c>
-      <c r="K318" s="7" t="s">
-        <v>664</v>
       </c>
       <c r="L318">
         <v>31000</v>
@@ -13436,7 +13432,7 @@
         <v>13</v>
       </c>
       <c r="C319" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D319" t="s">
         <v>15</v>
@@ -13445,10 +13441,10 @@
         <v>16</v>
       </c>
       <c r="J319" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="K319" s="7" t="s">
         <v>665</v>
-      </c>
-      <c r="K319" s="7" t="s">
-        <v>666</v>
       </c>
       <c r="L319">
         <v>31000</v>
@@ -13465,7 +13461,7 @@
         <v>13</v>
       </c>
       <c r="C320" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D320" t="s">
         <v>15</v>
@@ -13474,10 +13470,10 @@
         <v>16</v>
       </c>
       <c r="J320" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="K320" s="7" t="s">
         <v>667</v>
-      </c>
-      <c r="K320" s="7" t="s">
-        <v>668</v>
       </c>
       <c r="L320">
         <v>62000</v>
@@ -13494,7 +13490,7 @@
         <v>13</v>
       </c>
       <c r="C321" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D321" t="s">
         <v>15</v>
@@ -13503,10 +13499,10 @@
         <v>16</v>
       </c>
       <c r="J321" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="K321" s="7" t="s">
         <v>669</v>
-      </c>
-      <c r="K321" s="7" t="s">
-        <v>670</v>
       </c>
       <c r="L321">
         <v>46000</v>
@@ -13523,7 +13519,7 @@
         <v>13</v>
       </c>
       <c r="C322" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D322" t="s">
         <v>15</v>
@@ -13532,10 +13528,10 @@
         <v>16</v>
       </c>
       <c r="J322" s="23" t="s">
+        <v>670</v>
+      </c>
+      <c r="K322" s="7" t="s">
         <v>671</v>
-      </c>
-      <c r="K322" s="7" t="s">
-        <v>672</v>
       </c>
       <c r="L322">
         <v>155000</v>
@@ -13552,7 +13548,7 @@
         <v>13</v>
       </c>
       <c r="C323" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D323" t="s">
         <v>15</v>
@@ -13561,10 +13557,10 @@
         <v>16</v>
       </c>
       <c r="J323" s="23" t="s">
+        <v>672</v>
+      </c>
+      <c r="K323" s="7" t="s">
         <v>673</v>
-      </c>
-      <c r="K323" s="7" t="s">
-        <v>674</v>
       </c>
       <c r="L323">
         <v>115000</v>
@@ -13581,7 +13577,7 @@
         <v>13</v>
       </c>
       <c r="C324" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D324" t="s">
         <v>15</v>
@@ -13590,10 +13586,10 @@
         <v>16</v>
       </c>
       <c r="J324" s="23" t="s">
+        <v>674</v>
+      </c>
+      <c r="K324" s="7" t="s">
         <v>675</v>
-      </c>
-      <c r="K324" s="7" t="s">
-        <v>676</v>
       </c>
       <c r="L324">
         <v>432400</v>
@@ -13610,7 +13606,7 @@
         <v>13</v>
       </c>
       <c r="C325" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D325" t="s">
         <v>15</v>
@@ -13619,10 +13615,10 @@
         <v>16</v>
       </c>
       <c r="J325" s="23" t="s">
+        <v>676</v>
+      </c>
+      <c r="K325" s="7" t="s">
         <v>677</v>
-      </c>
-      <c r="K325" s="7" t="s">
-        <v>678</v>
       </c>
       <c r="L325">
         <v>155000</v>
@@ -13639,7 +13635,7 @@
         <v>13</v>
       </c>
       <c r="C326" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D326" t="s">
         <v>15</v>
@@ -13648,10 +13644,10 @@
         <v>16</v>
       </c>
       <c r="J326" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="K326" s="7" t="s">
         <v>679</v>
-      </c>
-      <c r="K326" s="7" t="s">
-        <v>680</v>
       </c>
       <c r="L326">
         <v>155000</v>
@@ -13668,7 +13664,7 @@
         <v>13</v>
       </c>
       <c r="C327" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D327" t="s">
         <v>15</v>
@@ -13677,10 +13673,10 @@
         <v>16</v>
       </c>
       <c r="J327" s="23" t="s">
+        <v>680</v>
+      </c>
+      <c r="K327" s="7" t="s">
         <v>681</v>
-      </c>
-      <c r="K327" s="7" t="s">
-        <v>682</v>
       </c>
       <c r="L327">
         <v>155000</v>
@@ -13697,7 +13693,7 @@
         <v>13</v>
       </c>
       <c r="C328" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D328" t="s">
         <v>15</v>
@@ -13706,10 +13702,10 @@
         <v>16</v>
       </c>
       <c r="J328" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="K328" s="7" t="s">
         <v>683</v>
-      </c>
-      <c r="K328" s="7" t="s">
-        <v>684</v>
       </c>
       <c r="L328">
         <v>115000</v>
@@ -13726,7 +13722,7 @@
         <v>13</v>
       </c>
       <c r="C329" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D329" t="s">
         <v>15</v>
@@ -13735,10 +13731,10 @@
         <v>16</v>
       </c>
       <c r="J329" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="K329" s="7" t="s">
         <v>685</v>
-      </c>
-      <c r="K329" s="7" t="s">
-        <v>686</v>
       </c>
       <c r="L329">
         <v>115000</v>
@@ -13755,7 +13751,7 @@
         <v>13</v>
       </c>
       <c r="C330" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D330" t="s">
         <v>15</v>
@@ -13764,10 +13760,10 @@
         <v>16</v>
       </c>
       <c r="J330" s="23" t="s">
+        <v>686</v>
+      </c>
+      <c r="K330" s="7" t="s">
         <v>687</v>
-      </c>
-      <c r="K330" s="7" t="s">
-        <v>688</v>
       </c>
       <c r="L330">
         <v>155000</v>
@@ -13784,7 +13780,7 @@
         <v>13</v>
       </c>
       <c r="C331" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D331" t="s">
         <v>15</v>
@@ -13793,10 +13789,10 @@
         <v>16</v>
       </c>
       <c r="J331" s="23" t="s">
+        <v>688</v>
+      </c>
+      <c r="K331" s="7" t="s">
         <v>689</v>
-      </c>
-      <c r="K331" s="7" t="s">
-        <v>690</v>
       </c>
       <c r="L331">
         <v>876770</v>
@@ -13813,7 +13809,7 @@
         <v>13</v>
       </c>
       <c r="C332" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D332" t="s">
         <v>15</v>
@@ -13822,10 +13818,10 @@
         <v>16</v>
       </c>
       <c r="J332" s="23" t="s">
+        <v>690</v>
+      </c>
+      <c r="K332" s="7" t="s">
         <v>691</v>
-      </c>
-      <c r="K332" s="7" t="s">
-        <v>692</v>
       </c>
       <c r="L332">
         <v>31000</v>
@@ -13840,7 +13836,7 @@
         <v>13</v>
       </c>
       <c r="C333" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D333" t="s">
         <v>15</v>
@@ -13849,10 +13845,10 @@
         <v>16</v>
       </c>
       <c r="J333" s="23" t="s">
+        <v>692</v>
+      </c>
+      <c r="K333" s="7" t="s">
         <v>693</v>
-      </c>
-      <c r="K333" s="7" t="s">
-        <v>694</v>
       </c>
       <c r="L333">
         <v>31000</v>
@@ -13869,7 +13865,7 @@
         <v>13</v>
       </c>
       <c r="C334" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D334" t="s">
         <v>15</v>
@@ -13878,10 +13874,10 @@
         <v>16</v>
       </c>
       <c r="J334" s="23" t="s">
+        <v>694</v>
+      </c>
+      <c r="K334" s="7" t="s">
         <v>695</v>
-      </c>
-      <c r="K334" s="7" t="s">
-        <v>696</v>
       </c>
       <c r="L334">
         <v>31000</v>
@@ -13898,7 +13894,7 @@
         <v>13</v>
       </c>
       <c r="C335" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D335" t="s">
         <v>15</v>
@@ -13907,10 +13903,10 @@
         <v>16</v>
       </c>
       <c r="J335" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="K335" s="7" t="s">
         <v>697</v>
-      </c>
-      <c r="K335" s="7" t="s">
-        <v>698</v>
       </c>
       <c r="L335">
         <v>31000</v>
@@ -13927,7 +13923,7 @@
         <v>13</v>
       </c>
       <c r="C336" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D336" t="s">
         <v>15</v>
@@ -13936,10 +13932,10 @@
         <v>16</v>
       </c>
       <c r="J336" s="23" t="s">
+        <v>698</v>
+      </c>
+      <c r="K336" s="7" t="s">
         <v>699</v>
-      </c>
-      <c r="K336" s="7" t="s">
-        <v>700</v>
       </c>
       <c r="L336">
         <v>31000</v>
@@ -13956,7 +13952,7 @@
         <v>13</v>
       </c>
       <c r="C337" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D337" t="s">
         <v>15</v>
@@ -13965,10 +13961,10 @@
         <v>16</v>
       </c>
       <c r="J337" s="23" t="s">
+        <v>700</v>
+      </c>
+      <c r="K337" s="7" t="s">
         <v>701</v>
-      </c>
-      <c r="K337" s="7" t="s">
-        <v>702</v>
       </c>
       <c r="L337">
         <v>31000</v>
@@ -13985,7 +13981,7 @@
         <v>13</v>
       </c>
       <c r="C338" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D338" t="s">
         <v>15</v>
@@ -13994,10 +13990,10 @@
         <v>16</v>
       </c>
       <c r="J338" s="23" t="s">
+        <v>702</v>
+      </c>
+      <c r="K338" s="7" t="s">
         <v>703</v>
-      </c>
-      <c r="K338" s="7" t="s">
-        <v>704</v>
       </c>
       <c r="L338">
         <v>31000</v>
@@ -14014,7 +14010,7 @@
         <v>13</v>
       </c>
       <c r="C339" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D339" t="s">
         <v>15</v>
@@ -14023,10 +14019,10 @@
         <v>16</v>
       </c>
       <c r="J339" s="23" t="s">
+        <v>704</v>
+      </c>
+      <c r="K339" s="7" t="s">
         <v>705</v>
-      </c>
-      <c r="K339" s="7" t="s">
-        <v>706</v>
       </c>
       <c r="L339">
         <v>31000</v>
@@ -14043,7 +14039,7 @@
         <v>13</v>
       </c>
       <c r="C340" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D340" t="s">
         <v>15</v>
@@ -14052,10 +14048,10 @@
         <v>16</v>
       </c>
       <c r="J340" s="23" t="s">
+        <v>706</v>
+      </c>
+      <c r="K340" s="7" t="s">
         <v>707</v>
-      </c>
-      <c r="K340" s="7" t="s">
-        <v>708</v>
       </c>
       <c r="L340">
         <v>31000</v>
@@ -14072,7 +14068,7 @@
         <v>13</v>
       </c>
       <c r="C341" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D341" t="s">
         <v>15</v>
@@ -14081,10 +14077,10 @@
         <v>16</v>
       </c>
       <c r="J341" s="23" t="s">
+        <v>708</v>
+      </c>
+      <c r="K341" s="7" t="s">
         <v>709</v>
-      </c>
-      <c r="K341" s="7" t="s">
-        <v>710</v>
       </c>
       <c r="L341">
         <v>31000</v>
@@ -14101,7 +14097,7 @@
         <v>13</v>
       </c>
       <c r="C342" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D342" t="s">
         <v>15</v>
@@ -14110,10 +14106,10 @@
         <v>16</v>
       </c>
       <c r="J342" s="23" t="s">
+        <v>710</v>
+      </c>
+      <c r="K342" s="7" t="s">
         <v>711</v>
-      </c>
-      <c r="K342" s="7" t="s">
-        <v>712</v>
       </c>
       <c r="L342">
         <v>23000</v>
@@ -14130,7 +14126,7 @@
         <v>13</v>
       </c>
       <c r="C343" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D343" t="s">
         <v>15</v>
@@ -14139,10 +14135,10 @@
         <v>16</v>
       </c>
       <c r="J343" s="23" t="s">
+        <v>712</v>
+      </c>
+      <c r="K343" s="7" t="s">
         <v>713</v>
-      </c>
-      <c r="K343" s="7" t="s">
-        <v>714</v>
       </c>
       <c r="L343">
         <v>31000</v>
@@ -14159,7 +14155,7 @@
         <v>13</v>
       </c>
       <c r="C344" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D344" t="s">
         <v>15</v>
@@ -14168,10 +14164,10 @@
         <v>16</v>
       </c>
       <c r="J344" s="23" t="s">
+        <v>714</v>
+      </c>
+      <c r="K344" s="7" t="s">
         <v>715</v>
-      </c>
-      <c r="K344" s="7" t="s">
-        <v>716</v>
       </c>
       <c r="L344">
         <v>198720</v>
@@ -14188,7 +14184,7 @@
         <v>13</v>
       </c>
       <c r="C345" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D345" t="s">
         <v>15</v>
@@ -14197,10 +14193,10 @@
         <v>16</v>
       </c>
       <c r="J345" s="23" t="s">
+        <v>716</v>
+      </c>
+      <c r="K345" s="7" t="s">
         <v>717</v>
-      </c>
-      <c r="K345" s="7" t="s">
-        <v>718</v>
       </c>
       <c r="L345">
         <v>31000</v>
@@ -14217,7 +14213,7 @@
         <v>13</v>
       </c>
       <c r="C346" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D346" t="s">
         <v>15</v>
@@ -14226,10 +14222,10 @@
         <v>16</v>
       </c>
       <c r="J346" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="K346" s="7" t="s">
         <v>719</v>
-      </c>
-      <c r="K346" s="7" t="s">
-        <v>720</v>
       </c>
       <c r="L346">
         <v>31000</v>
@@ -14246,7 +14242,7 @@
         <v>13</v>
       </c>
       <c r="C347" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D347" t="s">
         <v>15</v>
@@ -14255,10 +14251,10 @@
         <v>16</v>
       </c>
       <c r="J347" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="K347" s="7" t="s">
         <v>721</v>
-      </c>
-      <c r="K347" s="7" t="s">
-        <v>722</v>
       </c>
       <c r="L347">
         <v>31000</v>
@@ -14275,7 +14271,7 @@
         <v>13</v>
       </c>
       <c r="C348" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D348" t="s">
         <v>15</v>
@@ -14284,10 +14280,10 @@
         <v>16</v>
       </c>
       <c r="J348" s="23" t="s">
+        <v>722</v>
+      </c>
+      <c r="K348" s="7" t="s">
         <v>723</v>
-      </c>
-      <c r="K348" s="7" t="s">
-        <v>724</v>
       </c>
       <c r="L348">
         <v>1210720</v>
@@ -14304,7 +14300,7 @@
         <v>13</v>
       </c>
       <c r="C349" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D349" t="s">
         <v>15</v>
@@ -14313,10 +14309,10 @@
         <v>16</v>
       </c>
       <c r="J349" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="K349" s="7" t="s">
         <v>725</v>
-      </c>
-      <c r="K349" s="7" t="s">
-        <v>726</v>
       </c>
       <c r="L349">
         <v>772800</v>
@@ -14333,7 +14329,7 @@
         <v>13</v>
       </c>
       <c r="C350" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D350" t="s">
         <v>15</v>
@@ -14342,10 +14338,10 @@
         <v>16</v>
       </c>
       <c r="J350" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="K350" s="7" t="s">
         <v>727</v>
-      </c>
-      <c r="K350" s="7" t="s">
-        <v>728</v>
       </c>
       <c r="L350">
         <v>598000</v>
@@ -14362,7 +14358,7 @@
         <v>13</v>
       </c>
       <c r="C351" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D351" t="s">
         <v>15</v>
@@ -14371,10 +14367,10 @@
         <v>16</v>
       </c>
       <c r="J351" s="23" t="s">
+        <v>728</v>
+      </c>
+      <c r="K351" s="7" t="s">
         <v>729</v>
-      </c>
-      <c r="K351" s="7" t="s">
-        <v>730</v>
       </c>
       <c r="L351">
         <v>155000</v>
@@ -14391,7 +14387,7 @@
         <v>13</v>
       </c>
       <c r="C352" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D352" t="s">
         <v>15</v>
@@ -14400,10 +14396,10 @@
         <v>16</v>
       </c>
       <c r="J352" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="K352" s="7" t="s">
         <v>731</v>
-      </c>
-      <c r="K352" s="7" t="s">
-        <v>732</v>
       </c>
       <c r="L352">
         <v>214000</v>
@@ -14420,7 +14416,7 @@
         <v>13</v>
       </c>
       <c r="C353" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D353" t="s">
         <v>15</v>
@@ -14429,10 +14425,10 @@
         <v>16</v>
       </c>
       <c r="J353" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="K353" s="7" t="s">
         <v>733</v>
-      </c>
-      <c r="K353" s="7" t="s">
-        <v>734</v>
       </c>
       <c r="L353">
         <v>155000</v>
@@ -14449,7 +14445,7 @@
         <v>13</v>
       </c>
       <c r="C354" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D354" t="s">
         <v>15</v>
@@ -14458,10 +14454,10 @@
         <v>16</v>
       </c>
       <c r="J354" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="K354" s="7" t="s">
         <v>735</v>
-      </c>
-      <c r="K354" s="7" t="s">
-        <v>736</v>
       </c>
       <c r="L354">
         <v>155000</v>
@@ -14478,7 +14474,7 @@
         <v>13</v>
       </c>
       <c r="C355" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D355" t="s">
         <v>15</v>
@@ -14487,10 +14483,10 @@
         <v>16</v>
       </c>
       <c r="J355" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="K355" s="7" t="s">
         <v>737</v>
-      </c>
-      <c r="K355" s="7" t="s">
-        <v>738</v>
       </c>
       <c r="L355">
         <v>155000</v>
@@ -14507,7 +14503,7 @@
         <v>13</v>
       </c>
       <c r="C356" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D356" t="s">
         <v>15</v>
@@ -14516,10 +14512,10 @@
         <v>16</v>
       </c>
       <c r="J356" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="K356" s="7" t="s">
         <v>739</v>
-      </c>
-      <c r="K356" s="7" t="s">
-        <v>740</v>
       </c>
       <c r="L356">
         <v>155000</v>
@@ -14536,7 +14532,7 @@
         <v>13</v>
       </c>
       <c r="C357" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D357" t="s">
         <v>15</v>
@@ -14545,10 +14541,10 @@
         <v>16</v>
       </c>
       <c r="J357" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="K357" s="7" t="s">
         <v>741</v>
-      </c>
-      <c r="K357" s="7" t="s">
-        <v>742</v>
       </c>
       <c r="L357">
         <v>155000</v>
@@ -14565,7 +14561,7 @@
         <v>13</v>
       </c>
       <c r="C358" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D358" t="s">
         <v>15</v>
@@ -14574,10 +14570,10 @@
         <v>16</v>
       </c>
       <c r="J358" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="K358" s="7" t="s">
         <v>743</v>
-      </c>
-      <c r="K358" s="7" t="s">
-        <v>744</v>
       </c>
       <c r="L358">
         <v>155000</v>
@@ -14594,7 +14590,7 @@
         <v>13</v>
       </c>
       <c r="C359" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D359" t="s">
         <v>15</v>
@@ -14603,10 +14599,10 @@
         <v>16</v>
       </c>
       <c r="J359" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="K359" s="7" t="s">
         <v>745</v>
-      </c>
-      <c r="K359" s="7" t="s">
-        <v>746</v>
       </c>
       <c r="L359">
         <v>155000</v>
@@ -14623,7 +14619,7 @@
         <v>13</v>
       </c>
       <c r="C360" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D360" t="s">
         <v>15</v>
@@ -14632,10 +14628,10 @@
         <v>16</v>
       </c>
       <c r="J360" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="K360" s="7" t="s">
         <v>747</v>
-      </c>
-      <c r="K360" s="7" t="s">
-        <v>748</v>
       </c>
       <c r="L360">
         <v>401000</v>
@@ -14652,7 +14648,7 @@
         <v>13</v>
       </c>
       <c r="C361" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D361" t="s">
         <v>15</v>
@@ -14661,10 +14657,10 @@
         <v>16</v>
       </c>
       <c r="J361" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="K361" s="7" t="s">
         <v>749</v>
-      </c>
-      <c r="K361" s="7" t="s">
-        <v>750</v>
       </c>
       <c r="L361">
         <v>107000</v>
@@ -14681,7 +14677,7 @@
         <v>13</v>
       </c>
       <c r="C362" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D362" t="s">
         <v>15</v>
@@ -14690,10 +14686,10 @@
         <v>16</v>
       </c>
       <c r="J362" s="10" t="s">
+        <v>750</v>
+      </c>
+      <c r="K362" s="7" t="s">
         <v>751</v>
-      </c>
-      <c r="K362" s="7" t="s">
-        <v>752</v>
       </c>
       <c r="L362">
         <v>401000</v>
@@ -14710,7 +14706,7 @@
         <v>13</v>
       </c>
       <c r="C363" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D363" t="s">
         <v>15</v>
@@ -14719,10 +14715,10 @@
         <v>16</v>
       </c>
       <c r="J363" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="K363" s="7" t="s">
         <v>753</v>
-      </c>
-      <c r="K363" s="7" t="s">
-        <v>754</v>
       </c>
       <c r="L363">
         <v>214000</v>
@@ -14739,7 +14735,7 @@
         <v>13</v>
       </c>
       <c r="C364" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D364" t="s">
         <v>15</v>
@@ -14748,10 +14744,10 @@
         <v>16</v>
       </c>
       <c r="J364" s="10" t="s">
+        <v>754</v>
+      </c>
+      <c r="K364" s="7" t="s">
         <v>755</v>
-      </c>
-      <c r="K364" s="7" t="s">
-        <v>756</v>
       </c>
       <c r="L364">
         <v>214000</v>
@@ -14768,7 +14764,7 @@
         <v>13</v>
       </c>
       <c r="C365" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D365" t="s">
         <v>15</v>
@@ -14777,10 +14773,10 @@
         <v>16</v>
       </c>
       <c r="J365" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="K365" s="7" t="s">
         <v>757</v>
-      </c>
-      <c r="K365" s="7" t="s">
-        <v>758</v>
       </c>
       <c r="L365">
         <v>214000</v>
@@ -14797,7 +14793,7 @@
         <v>13</v>
       </c>
       <c r="C366" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D366" t="s">
         <v>15</v>
@@ -14806,10 +14802,10 @@
         <v>16</v>
       </c>
       <c r="J366" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="K366" s="7" t="s">
         <v>759</v>
-      </c>
-      <c r="K366" s="7" t="s">
-        <v>760</v>
       </c>
       <c r="L366">
         <v>214000</v>
@@ -14826,7 +14822,7 @@
         <v>13</v>
       </c>
       <c r="C367" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D367" t="s">
         <v>15</v>
@@ -14835,10 +14831,10 @@
         <v>16</v>
       </c>
       <c r="J367" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="K367" s="7" t="s">
         <v>761</v>
-      </c>
-      <c r="K367" s="7" t="s">
-        <v>762</v>
       </c>
       <c r="L367">
         <v>400000</v>
@@ -14855,7 +14851,7 @@
         <v>13</v>
       </c>
       <c r="C368" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D368" t="s">
         <v>15</v>
@@ -14864,10 +14860,10 @@
         <v>16</v>
       </c>
       <c r="J368" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="K368" s="7" t="s">
         <v>763</v>
-      </c>
-      <c r="K368" s="7" t="s">
-        <v>764</v>
       </c>
       <c r="L368">
         <v>214000</v>
@@ -14884,7 +14880,7 @@
         <v>13</v>
       </c>
       <c r="C369" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D369" t="s">
         <v>15</v>
@@ -14893,10 +14889,10 @@
         <v>16</v>
       </c>
       <c r="J369" s="10" t="s">
+        <v>764</v>
+      </c>
+      <c r="K369" s="7" t="s">
         <v>765</v>
-      </c>
-      <c r="K369" s="7" t="s">
-        <v>766</v>
       </c>
       <c r="L369">
         <v>400000</v>
@@ -14913,7 +14909,7 @@
         <v>13</v>
       </c>
       <c r="C370" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D370" t="s">
         <v>15</v>
@@ -14922,10 +14918,10 @@
         <v>16</v>
       </c>
       <c r="J370" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="K370" s="7" t="s">
         <v>767</v>
-      </c>
-      <c r="K370" s="7" t="s">
-        <v>768</v>
       </c>
       <c r="L370">
         <v>214000</v>
@@ -14942,7 +14938,7 @@
         <v>13</v>
       </c>
       <c r="C371" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D371" t="s">
         <v>15</v>
@@ -14951,10 +14947,10 @@
         <v>16</v>
       </c>
       <c r="J371" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="K371" s="7" t="s">
         <v>769</v>
-      </c>
-      <c r="K371" s="7" t="s">
-        <v>770</v>
       </c>
       <c r="L371">
         <v>214000</v>
@@ -14971,7 +14967,7 @@
         <v>13</v>
       </c>
       <c r="C372" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D372" t="s">
         <v>15</v>
@@ -14980,10 +14976,10 @@
         <v>16</v>
       </c>
       <c r="J372" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="K372" s="7" t="s">
         <v>771</v>
-      </c>
-      <c r="K372" s="7" t="s">
-        <v>772</v>
       </c>
       <c r="L372">
         <v>214000</v>
@@ -15000,7 +14996,7 @@
         <v>13</v>
       </c>
       <c r="C373" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D373" t="s">
         <v>15</v>
@@ -15009,10 +15005,10 @@
         <v>16</v>
       </c>
       <c r="J373" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="K373" s="7" t="s">
         <v>773</v>
-      </c>
-      <c r="K373" s="7" t="s">
-        <v>774</v>
       </c>
       <c r="L373">
         <v>214000</v>
@@ -15029,7 +15025,7 @@
         <v>13</v>
       </c>
       <c r="C374" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D374" t="s">
         <v>15</v>
@@ -15038,10 +15034,10 @@
         <v>16</v>
       </c>
       <c r="J374" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="K374" s="7" t="s">
         <v>775</v>
-      </c>
-      <c r="K374" s="7" t="s">
-        <v>776</v>
       </c>
       <c r="L374">
         <v>214000</v>
@@ -15058,7 +15054,7 @@
         <v>13</v>
       </c>
       <c r="C375" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D375" t="s">
         <v>15</v>
@@ -15067,10 +15063,10 @@
         <v>16</v>
       </c>
       <c r="J375" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="K375" s="7" t="s">
         <v>777</v>
-      </c>
-      <c r="K375" s="7" t="s">
-        <v>778</v>
       </c>
       <c r="L375">
         <v>214000</v>
@@ -15087,7 +15083,7 @@
         <v>13</v>
       </c>
       <c r="C376" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D376" t="s">
         <v>15</v>
@@ -15096,10 +15092,10 @@
         <v>16</v>
       </c>
       <c r="J376" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="K376" s="7" t="s">
         <v>779</v>
-      </c>
-      <c r="K376" s="7" t="s">
-        <v>780</v>
       </c>
       <c r="L376">
         <v>214000</v>
@@ -15116,7 +15112,7 @@
         <v>13</v>
       </c>
       <c r="C377" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D377" t="s">
         <v>15</v>
@@ -15125,10 +15121,10 @@
         <v>16</v>
       </c>
       <c r="J377" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="K377" s="7" t="s">
         <v>781</v>
-      </c>
-      <c r="K377" s="7" t="s">
-        <v>782</v>
       </c>
       <c r="L377">
         <v>214000</v>
@@ -15145,7 +15141,7 @@
         <v>13</v>
       </c>
       <c r="C378" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D378" t="s">
         <v>15</v>
@@ -15154,10 +15150,10 @@
         <v>16</v>
       </c>
       <c r="J378" s="10" t="s">
+        <v>782</v>
+      </c>
+      <c r="K378" s="7" t="s">
         <v>783</v>
-      </c>
-      <c r="K378" s="7" t="s">
-        <v>784</v>
       </c>
       <c r="L378">
         <v>214000</v>
@@ -15174,7 +15170,7 @@
         <v>13</v>
       </c>
       <c r="C379" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D379" t="s">
         <v>15</v>
@@ -15183,10 +15179,10 @@
         <v>16</v>
       </c>
       <c r="J379" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="K379" s="7" t="s">
         <v>785</v>
-      </c>
-      <c r="K379" s="7" t="s">
-        <v>786</v>
       </c>
       <c r="L379">
         <v>214000</v>
@@ -15203,7 +15199,7 @@
         <v>13</v>
       </c>
       <c r="C380" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D380" t="s">
         <v>15</v>
@@ -15212,10 +15208,10 @@
         <v>16</v>
       </c>
       <c r="J380" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="K380" s="7" t="s">
         <v>787</v>
-      </c>
-      <c r="K380" s="7" t="s">
-        <v>788</v>
       </c>
       <c r="L380">
         <v>155000</v>
@@ -15232,7 +15228,7 @@
         <v>13</v>
       </c>
       <c r="C381" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D381" t="s">
         <v>15</v>
@@ -15241,10 +15237,10 @@
         <v>16</v>
       </c>
       <c r="J381" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="K381" s="7" t="s">
         <v>789</v>
-      </c>
-      <c r="K381" s="7" t="s">
-        <v>790</v>
       </c>
       <c r="L381">
         <v>155000</v>
@@ -15261,7 +15257,7 @@
         <v>13</v>
       </c>
       <c r="C382" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D382" t="s">
         <v>15</v>
@@ -15270,10 +15266,10 @@
         <v>16</v>
       </c>
       <c r="J382" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="K382" s="7" t="s">
         <v>791</v>
-      </c>
-      <c r="K382" s="7" t="s">
-        <v>792</v>
       </c>
       <c r="L382">
         <v>322000</v>
@@ -15290,7 +15286,7 @@
         <v>13</v>
       </c>
       <c r="C383" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D383" t="s">
         <v>15</v>
@@ -15299,10 +15295,10 @@
         <v>16</v>
       </c>
       <c r="J383" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="K383" s="7" t="s">
         <v>793</v>
-      </c>
-      <c r="K383" s="7" t="s">
-        <v>794</v>
       </c>
       <c r="L383">
         <v>155000</v>
@@ -15319,7 +15315,7 @@
         <v>13</v>
       </c>
       <c r="C384" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D384" t="s">
         <v>15</v>
@@ -15328,10 +15324,10 @@
         <v>16</v>
       </c>
       <c r="J384" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="K384" s="7" t="s">
         <v>795</v>
-      </c>
-      <c r="K384" s="7" t="s">
-        <v>796</v>
       </c>
       <c r="L384">
         <v>155000</v>
@@ -15348,7 +15344,7 @@
         <v>13</v>
       </c>
       <c r="C385" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D385" t="s">
         <v>15</v>
@@ -15357,10 +15353,10 @@
         <v>16</v>
       </c>
       <c r="J385" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="K385" s="7" t="s">
         <v>797</v>
-      </c>
-      <c r="K385" s="7" t="s">
-        <v>798</v>
       </c>
       <c r="L385">
         <v>155000</v>
@@ -15377,7 +15373,7 @@
         <v>13</v>
       </c>
       <c r="C386" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D386" t="s">
         <v>15</v>
@@ -15386,10 +15382,10 @@
         <v>16</v>
       </c>
       <c r="J386" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="K386" s="7" t="s">
         <v>799</v>
-      </c>
-      <c r="K386" s="7" t="s">
-        <v>800</v>
       </c>
       <c r="L386">
         <v>155000</v>
@@ -15406,7 +15402,7 @@
         <v>13</v>
       </c>
       <c r="C387" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D387" t="s">
         <v>15</v>
@@ -15415,10 +15411,10 @@
         <v>16</v>
       </c>
       <c r="J387" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="K387" s="7" t="s">
         <v>801</v>
-      </c>
-      <c r="K387" s="7" t="s">
-        <v>802</v>
       </c>
       <c r="L387">
         <v>155000</v>
@@ -15435,7 +15431,7 @@
         <v>13</v>
       </c>
       <c r="C388" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D388" t="s">
         <v>15</v>
@@ -15444,10 +15440,10 @@
         <v>16</v>
       </c>
       <c r="J388" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="K388" s="7" t="s">
         <v>803</v>
-      </c>
-      <c r="K388" s="7" t="s">
-        <v>804</v>
       </c>
       <c r="L388">
         <v>155000</v>
@@ -15464,7 +15460,7 @@
         <v>13</v>
       </c>
       <c r="C389" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D389" t="s">
         <v>15</v>
@@ -15473,10 +15469,10 @@
         <v>16</v>
       </c>
       <c r="J389" s="10" t="s">
+        <v>804</v>
+      </c>
+      <c r="K389" s="7" t="s">
         <v>805</v>
-      </c>
-      <c r="K389" s="7" t="s">
-        <v>806</v>
       </c>
       <c r="L389">
         <v>155000</v>
@@ -15493,7 +15489,7 @@
         <v>13</v>
       </c>
       <c r="C390" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D390" t="s">
         <v>15</v>
@@ -15502,10 +15498,10 @@
         <v>16</v>
       </c>
       <c r="J390" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="K390" s="7" t="s">
         <v>807</v>
-      </c>
-      <c r="K390" s="7" t="s">
-        <v>808</v>
       </c>
       <c r="L390">
         <v>276716</v>
@@ -15522,7 +15518,7 @@
         <v>13</v>
       </c>
       <c r="C391" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D391" t="s">
         <v>15</v>
@@ -15531,10 +15527,10 @@
         <v>16</v>
       </c>
       <c r="J391" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="K391" s="7" t="s">
         <v>809</v>
-      </c>
-      <c r="K391" s="7" t="s">
-        <v>810</v>
       </c>
       <c r="L391">
         <v>248240</v>
@@ -15551,7 +15547,7 @@
         <v>13</v>
       </c>
       <c r="C392" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D392" t="s">
         <v>15</v>
@@ -15560,10 +15556,10 @@
         <v>16</v>
       </c>
       <c r="J392" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="K392" s="7" t="s">
         <v>811</v>
-      </c>
-      <c r="K392" s="7" t="s">
-        <v>812</v>
       </c>
       <c r="L392">
         <v>465160</v>
@@ -15580,7 +15576,7 @@
         <v>13</v>
       </c>
       <c r="C393" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D393" t="s">
         <v>15</v>
@@ -15589,10 +15585,10 @@
         <v>16</v>
       </c>
       <c r="J393" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="K393" s="7" t="s">
         <v>813</v>
-      </c>
-      <c r="K393" s="7" t="s">
-        <v>814</v>
       </c>
       <c r="L393">
         <v>248240</v>
@@ -15609,7 +15605,7 @@
         <v>13</v>
       </c>
       <c r="C394" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D394" t="s">
         <v>15</v>
@@ -15618,10 +15614,10 @@
         <v>16</v>
       </c>
       <c r="J394" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="K394" s="7" t="s">
         <v>815</v>
-      </c>
-      <c r="K394" s="7" t="s">
-        <v>816</v>
       </c>
       <c r="L394">
         <v>465160</v>
@@ -15638,7 +15634,7 @@
         <v>13</v>
       </c>
       <c r="C395" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D395" t="s">
         <v>15</v>
@@ -15647,10 +15643,10 @@
         <v>16</v>
       </c>
       <c r="J395" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="K395" s="7" t="s">
         <v>817</v>
-      </c>
-      <c r="K395" s="7" t="s">
-        <v>818</v>
       </c>
       <c r="L395">
         <v>248240</v>
@@ -15667,7 +15663,7 @@
         <v>13</v>
       </c>
       <c r="C396" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D396" t="s">
         <v>15</v>
@@ -15676,10 +15672,10 @@
         <v>16</v>
       </c>
       <c r="J396" s="10" t="s">
+        <v>818</v>
+      </c>
+      <c r="K396" s="7" t="s">
         <v>819</v>
-      </c>
-      <c r="K396" s="7" t="s">
-        <v>820</v>
       </c>
       <c r="L396">
         <v>465160</v>
@@ -15696,7 +15692,7 @@
         <v>13</v>
       </c>
       <c r="C397" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D397" t="s">
         <v>15</v>
@@ -15705,10 +15701,10 @@
         <v>16</v>
       </c>
       <c r="J397" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="K397" s="7" t="s">
         <v>821</v>
-      </c>
-      <c r="K397" s="7" t="s">
-        <v>822</v>
       </c>
       <c r="L397">
         <v>248240</v>
@@ -15725,7 +15721,7 @@
         <v>13</v>
       </c>
       <c r="C398" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D398" t="s">
         <v>15</v>
@@ -15734,10 +15730,10 @@
         <v>16</v>
       </c>
       <c r="J398" s="10" t="s">
+        <v>822</v>
+      </c>
+      <c r="K398" s="7" t="s">
         <v>823</v>
-      </c>
-      <c r="K398" s="7" t="s">
-        <v>824</v>
       </c>
       <c r="L398">
         <v>248240</v>
@@ -15754,7 +15750,7 @@
         <v>13</v>
       </c>
       <c r="C399" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D399" t="s">
         <v>15</v>
@@ -15763,10 +15759,10 @@
         <v>16</v>
       </c>
       <c r="J399" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="K399" s="7" t="s">
         <v>825</v>
-      </c>
-      <c r="K399" s="7" t="s">
-        <v>826</v>
       </c>
       <c r="L399">
         <v>465160</v>
@@ -15783,7 +15779,7 @@
         <v>13</v>
       </c>
       <c r="C400" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D400" t="s">
         <v>15</v>
@@ -15792,10 +15788,10 @@
         <v>16</v>
       </c>
       <c r="J400" s="10" t="s">
+        <v>826</v>
+      </c>
+      <c r="K400" s="7" t="s">
         <v>827</v>
-      </c>
-      <c r="K400" s="7" t="s">
-        <v>828</v>
       </c>
       <c r="L400">
         <v>248240</v>
@@ -15812,7 +15808,7 @@
         <v>13</v>
       </c>
       <c r="C401" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D401" t="s">
         <v>15</v>
@@ -15821,10 +15817,10 @@
         <v>16</v>
       </c>
       <c r="J401" s="10" t="s">
+        <v>828</v>
+      </c>
+      <c r="K401" s="7" t="s">
         <v>829</v>
-      </c>
-      <c r="K401" s="7" t="s">
-        <v>830</v>
       </c>
       <c r="L401">
         <v>248240</v>
@@ -15841,7 +15837,7 @@
         <v>13</v>
       </c>
       <c r="C402" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D402" t="s">
         <v>15</v>
@@ -15850,10 +15846,10 @@
         <v>16</v>
       </c>
       <c r="J402" s="10" t="s">
+        <v>830</v>
+      </c>
+      <c r="K402" s="7" t="s">
         <v>831</v>
-      </c>
-      <c r="K402" s="7" t="s">
-        <v>832</v>
       </c>
       <c r="L402">
         <v>248240</v>
@@ -15870,7 +15866,7 @@
         <v>13</v>
       </c>
       <c r="C403" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D403" t="s">
         <v>15</v>
@@ -15879,10 +15875,10 @@
         <v>16</v>
       </c>
       <c r="J403" s="10" t="s">
+        <v>832</v>
+      </c>
+      <c r="K403" s="7" t="s">
         <v>833</v>
-      </c>
-      <c r="K403" s="7" t="s">
-        <v>834</v>
       </c>
       <c r="L403">
         <v>248240</v>
@@ -15899,7 +15895,7 @@
         <v>13</v>
       </c>
       <c r="C404" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D404" t="s">
         <v>15</v>
@@ -15908,10 +15904,10 @@
         <v>16</v>
       </c>
       <c r="J404" s="10" t="s">
+        <v>834</v>
+      </c>
+      <c r="K404" s="7" t="s">
         <v>835</v>
-      </c>
-      <c r="K404" s="7" t="s">
-        <v>836</v>
       </c>
       <c r="L404">
         <v>465160</v>
@@ -15928,7 +15924,7 @@
         <v>13</v>
       </c>
       <c r="C405" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D405" t="s">
         <v>15</v>
@@ -15937,10 +15933,10 @@
         <v>16</v>
       </c>
       <c r="J405" s="10" t="s">
+        <v>836</v>
+      </c>
+      <c r="K405" s="7" t="s">
         <v>837</v>
-      </c>
-      <c r="K405" s="7" t="s">
-        <v>838</v>
       </c>
       <c r="L405">
         <v>248240</v>
@@ -15957,7 +15953,7 @@
         <v>13</v>
       </c>
       <c r="C406" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D406" t="s">
         <v>15</v>
@@ -15966,10 +15962,10 @@
         <v>16</v>
       </c>
       <c r="J406" s="10" t="s">
+        <v>838</v>
+      </c>
+      <c r="K406" s="7" t="s">
         <v>839</v>
-      </c>
-      <c r="K406" s="7" t="s">
-        <v>840</v>
       </c>
       <c r="L406">
         <v>465160</v>
@@ -15986,7 +15982,7 @@
         <v>13</v>
       </c>
       <c r="C407" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D407" t="s">
         <v>15</v>
@@ -15995,10 +15991,10 @@
         <v>16</v>
       </c>
       <c r="J407" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="K407" s="7" t="s">
         <v>841</v>
-      </c>
-      <c r="K407" s="7" t="s">
-        <v>842</v>
       </c>
       <c r="L407">
         <v>248240</v>
@@ -16015,7 +16011,7 @@
         <v>13</v>
       </c>
       <c r="C408" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D408" t="s">
         <v>15</v>
@@ -16024,10 +16020,10 @@
         <v>16</v>
       </c>
       <c r="J408" s="6" t="s">
+        <v>842</v>
+      </c>
+      <c r="K408" s="7" t="s">
         <v>843</v>
-      </c>
-      <c r="K408" s="7" t="s">
-        <v>844</v>
       </c>
       <c r="L408">
         <v>248240</v>
@@ -16044,7 +16040,7 @@
         <v>13</v>
       </c>
       <c r="C409" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D409" t="s">
         <v>15</v>
@@ -16053,10 +16049,10 @@
         <v>16</v>
       </c>
       <c r="J409" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="K409" s="7" t="s">
         <v>845</v>
-      </c>
-      <c r="K409" s="7" t="s">
-        <v>846</v>
       </c>
       <c r="L409">
         <v>248240</v>
@@ -16073,7 +16069,7 @@
         <v>13</v>
       </c>
       <c r="C410" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D410" t="s">
         <v>15</v>
@@ -16082,10 +16078,10 @@
         <v>16</v>
       </c>
       <c r="J410" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="K410" s="7" t="s">
         <v>847</v>
-      </c>
-      <c r="K410" s="7" t="s">
-        <v>848</v>
       </c>
       <c r="L410">
         <v>465160</v>
@@ -16102,7 +16098,7 @@
         <v>13</v>
       </c>
       <c r="C411" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D411" t="s">
         <v>15</v>
@@ -16111,10 +16107,10 @@
         <v>16</v>
       </c>
       <c r="J411" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="K411" s="7" t="s">
         <v>849</v>
-      </c>
-      <c r="K411" s="7" t="s">
-        <v>850</v>
       </c>
       <c r="L411">
         <v>465160</v>
@@ -16131,7 +16127,7 @@
         <v>13</v>
       </c>
       <c r="C412" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D412" t="s">
         <v>15</v>
@@ -16140,10 +16136,10 @@
         <v>16</v>
       </c>
       <c r="J412" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="K412" s="7" t="s">
         <v>851</v>
-      </c>
-      <c r="K412" s="7" t="s">
-        <v>852</v>
       </c>
       <c r="L412">
         <v>248240</v>
@@ -16160,7 +16156,7 @@
         <v>13</v>
       </c>
       <c r="C413" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D413" t="s">
         <v>15</v>
@@ -16169,10 +16165,10 @@
         <v>16</v>
       </c>
       <c r="J413" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="K413" s="7" t="s">
         <v>853</v>
-      </c>
-      <c r="K413" s="7" t="s">
-        <v>854</v>
       </c>
       <c r="L413">
         <v>684140</v>
@@ -16189,7 +16185,7 @@
         <v>13</v>
       </c>
       <c r="C414" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D414" t="s">
         <v>15</v>
@@ -16198,10 +16194,10 @@
         <v>16</v>
       </c>
       <c r="J414" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="K414" s="7" t="s">
         <v>855</v>
-      </c>
-      <c r="K414" s="7" t="s">
-        <v>856</v>
       </c>
       <c r="L414">
         <v>277986</v>
@@ -16218,7 +16214,7 @@
         <v>13</v>
       </c>
       <c r="C415" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D415" t="s">
         <v>15</v>
@@ -16227,10 +16223,10 @@
         <v>16</v>
       </c>
       <c r="J415" s="6" t="s">
+        <v>856</v>
+      </c>
+      <c r="K415" s="7" t="s">
         <v>857</v>
-      </c>
-      <c r="K415" s="7" t="s">
-        <v>858</v>
       </c>
       <c r="L415">
         <v>277986</v>
@@ -16247,7 +16243,7 @@
         <v>13</v>
       </c>
       <c r="C416" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D416" t="s">
         <v>15</v>
@@ -16256,10 +16252,10 @@
         <v>16</v>
       </c>
       <c r="J416" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="K416" s="7" t="s">
         <v>859</v>
-      </c>
-      <c r="K416" s="7" t="s">
-        <v>860</v>
       </c>
       <c r="L416">
         <v>684140</v>
@@ -16276,7 +16272,7 @@
         <v>13</v>
       </c>
       <c r="C417" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D417" t="s">
         <v>15</v>
@@ -16285,10 +16281,10 @@
         <v>16</v>
       </c>
       <c r="J417" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="K417" s="7" t="s">
         <v>861</v>
-      </c>
-      <c r="K417" s="7" t="s">
-        <v>862</v>
       </c>
       <c r="L417">
         <v>277986</v>
@@ -16305,7 +16301,7 @@
         <v>13</v>
       </c>
       <c r="C418" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D418" t="s">
         <v>15</v>
@@ -16314,10 +16310,10 @@
         <v>16</v>
       </c>
       <c r="J418" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="K418" s="7" t="s">
         <v>863</v>
-      </c>
-      <c r="K418" s="7" t="s">
-        <v>864</v>
       </c>
       <c r="L418">
         <v>277986</v>
@@ -16334,7 +16330,7 @@
         <v>13</v>
       </c>
       <c r="C419" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D419" t="s">
         <v>15</v>
@@ -16343,10 +16339,10 @@
         <v>16</v>
       </c>
       <c r="J419" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="K419" s="7" t="s">
         <v>865</v>
-      </c>
-      <c r="K419" s="7" t="s">
-        <v>866</v>
       </c>
       <c r="L419">
         <v>277986</v>
@@ -16363,7 +16359,7 @@
         <v>13</v>
       </c>
       <c r="C420" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D420" t="s">
         <v>15</v>
@@ -16372,10 +16368,10 @@
         <v>16</v>
       </c>
       <c r="J420" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="K420" s="7" t="s">
         <v>867</v>
-      </c>
-      <c r="K420" s="7" t="s">
-        <v>868</v>
       </c>
       <c r="L420">
         <v>138993</v>
@@ -16392,7 +16388,7 @@
         <v>13</v>
       </c>
       <c r="C421" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D421" t="s">
         <v>15</v>
@@ -16401,10 +16397,10 @@
         <v>16</v>
       </c>
       <c r="J421" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="K421" s="7" t="s">
         <v>869</v>
-      </c>
-      <c r="K421" s="7" t="s">
-        <v>870</v>
       </c>
       <c r="L421">
         <v>278200</v>
@@ -16421,7 +16417,7 @@
         <v>13</v>
       </c>
       <c r="C422" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D422" t="s">
         <v>15</v>
@@ -16430,10 +16426,10 @@
         <v>16</v>
       </c>
       <c r="J422" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="K422" s="7" t="s">
         <v>871</v>
-      </c>
-      <c r="K422" s="7" t="s">
-        <v>872</v>
       </c>
       <c r="L422">
         <v>278200</v>
@@ -16450,7 +16446,7 @@
         <v>13</v>
       </c>
       <c r="C423" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D423" t="s">
         <v>15</v>
@@ -16459,10 +16455,10 @@
         <v>16</v>
       </c>
       <c r="J423" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="K423" s="7" t="s">
         <v>873</v>
-      </c>
-      <c r="K423" s="7" t="s">
-        <v>874</v>
       </c>
       <c r="L423">
         <v>278200</v>
@@ -16479,7 +16475,7 @@
         <v>13</v>
       </c>
       <c r="C424" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D424" t="s">
         <v>15</v>
@@ -16488,10 +16484,10 @@
         <v>16</v>
       </c>
       <c r="J424" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="K424" s="7" t="s">
         <v>875</v>
-      </c>
-      <c r="K424" s="7" t="s">
-        <v>876</v>
       </c>
       <c r="L424">
         <v>278200</v>
@@ -16508,7 +16504,7 @@
         <v>13</v>
       </c>
       <c r="C425" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D425" t="s">
         <v>15</v>
@@ -16517,10 +16513,10 @@
         <v>16</v>
       </c>
       <c r="J425" s="12" t="s">
+        <v>876</v>
+      </c>
+      <c r="K425" s="7" t="s">
         <v>877</v>
-      </c>
-      <c r="K425" s="7" t="s">
-        <v>878</v>
       </c>
       <c r="L425">
         <v>278200</v>
@@ -16537,7 +16533,7 @@
         <v>13</v>
       </c>
       <c r="C426" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D426" t="s">
         <v>15</v>
@@ -16546,10 +16542,10 @@
         <v>16</v>
       </c>
       <c r="J426" s="26" t="s">
+        <v>878</v>
+      </c>
+      <c r="K426" s="7" t="s">
         <v>879</v>
-      </c>
-      <c r="K426" s="7" t="s">
-        <v>880</v>
       </c>
       <c r="L426">
         <v>278200</v>
@@ -16566,7 +16562,7 @@
         <v>13</v>
       </c>
       <c r="C427" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D427" t="s">
         <v>15</v>
@@ -16575,10 +16571,10 @@
         <v>16</v>
       </c>
       <c r="J427" s="26" t="s">
+        <v>880</v>
+      </c>
+      <c r="K427" s="7" t="s">
         <v>881</v>
-      </c>
-      <c r="K427" s="7" t="s">
-        <v>882</v>
       </c>
       <c r="L427">
         <v>278200</v>
@@ -16595,7 +16591,7 @@
         <v>13</v>
       </c>
       <c r="C428" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D428" t="s">
         <v>15</v>
@@ -16604,10 +16600,10 @@
         <v>16</v>
       </c>
       <c r="J428" s="26" t="s">
+        <v>882</v>
+      </c>
+      <c r="K428" s="7" t="s">
         <v>883</v>
-      </c>
-      <c r="K428" s="7" t="s">
-        <v>884</v>
       </c>
       <c r="L428">
         <v>684660</v>
@@ -16624,7 +16620,7 @@
         <v>13</v>
       </c>
       <c r="C429" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D429" t="s">
         <v>15</v>
@@ -16633,10 +16629,10 @@
         <v>16</v>
       </c>
       <c r="J429" s="12" t="s">
+        <v>884</v>
+      </c>
+      <c r="K429" s="7" t="s">
         <v>885</v>
-      </c>
-      <c r="K429" s="7" t="s">
-        <v>886</v>
       </c>
       <c r="L429">
         <v>278200</v>
@@ -16653,7 +16649,7 @@
         <v>13</v>
       </c>
       <c r="C430" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D430" t="s">
         <v>15</v>
@@ -16662,10 +16658,10 @@
         <v>16</v>
       </c>
       <c r="J430" s="12" t="s">
+        <v>886</v>
+      </c>
+      <c r="K430" s="7" t="s">
         <v>887</v>
-      </c>
-      <c r="K430" s="7" t="s">
-        <v>888</v>
       </c>
       <c r="L430">
         <v>278200</v>
@@ -16682,7 +16678,7 @@
         <v>13</v>
       </c>
       <c r="C431" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D431" t="s">
         <v>15</v>
@@ -16691,10 +16687,10 @@
         <v>16</v>
       </c>
       <c r="J431" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="K431" s="7" t="s">
         <v>889</v>
-      </c>
-      <c r="K431" s="7" t="s">
-        <v>890</v>
       </c>
       <c r="L431">
         <v>542809</v>
@@ -16711,7 +16707,7 @@
         <v>13</v>
       </c>
       <c r="C432" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D432" t="s">
         <v>15</v>
@@ -16720,10 +16716,10 @@
         <v>16</v>
       </c>
       <c r="J432" s="12" t="s">
+        <v>890</v>
+      </c>
+      <c r="K432" s="7" t="s">
         <v>891</v>
-      </c>
-      <c r="K432" s="7" t="s">
-        <v>892</v>
       </c>
       <c r="L432">
         <v>308754</v>
@@ -16740,7 +16736,7 @@
         <v>13</v>
       </c>
       <c r="C433" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D433" t="s">
         <v>15</v>
@@ -16749,10 +16745,10 @@
         <v>16</v>
       </c>
       <c r="J433" s="12" t="s">
+        <v>892</v>
+      </c>
+      <c r="K433" s="7" t="s">
         <v>893</v>
-      </c>
-      <c r="K433" s="7" t="s">
-        <v>894</v>
       </c>
       <c r="L433">
         <v>308754</v>
@@ -16769,7 +16765,7 @@
         <v>13</v>
       </c>
       <c r="C434" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D434" t="s">
         <v>15</v>
@@ -16778,10 +16774,10 @@
         <v>16</v>
       </c>
       <c r="J434" s="12" t="s">
+        <v>894</v>
+      </c>
+      <c r="K434" s="7" t="s">
         <v>895</v>
-      </c>
-      <c r="K434" s="7" t="s">
-        <v>896</v>
       </c>
       <c r="L434">
         <v>308754</v>
@@ -16798,7 +16794,7 @@
         <v>13</v>
       </c>
       <c r="C435" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D435" t="s">
         <v>15</v>
@@ -16807,10 +16803,10 @@
         <v>16</v>
       </c>
       <c r="J435" s="29" t="s">
+        <v>896</v>
+      </c>
+      <c r="K435" s="7" t="s">
         <v>897</v>
-      </c>
-      <c r="K435" s="7" t="s">
-        <v>898</v>
       </c>
       <c r="L435">
         <v>308754</v>
@@ -16827,7 +16823,7 @@
         <v>13</v>
       </c>
       <c r="C436" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D436" t="s">
         <v>15</v>
@@ -16836,10 +16832,10 @@
         <v>16</v>
       </c>
       <c r="J436" s="29" t="s">
+        <v>898</v>
+      </c>
+      <c r="K436" s="7" t="s">
         <v>899</v>
-      </c>
-      <c r="K436" s="7" t="s">
-        <v>900</v>
       </c>
       <c r="L436">
         <v>308754</v>
@@ -16856,7 +16852,7 @@
         <v>13</v>
       </c>
       <c r="C437" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D437" t="s">
         <v>15</v>
@@ -16865,10 +16861,10 @@
         <v>16</v>
       </c>
       <c r="J437" s="29" t="s">
+        <v>900</v>
+      </c>
+      <c r="K437" s="7" t="s">
         <v>901</v>
-      </c>
-      <c r="K437" s="7" t="s">
-        <v>902</v>
       </c>
       <c r="L437">
         <v>542809</v>
@@ -16885,7 +16881,7 @@
         <v>13</v>
       </c>
       <c r="C438" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D438" t="s">
         <v>15</v>
@@ -16894,10 +16890,10 @@
         <v>16</v>
       </c>
       <c r="J438" s="29" t="s">
+        <v>902</v>
+      </c>
+      <c r="K438" s="7" t="s">
         <v>903</v>
-      </c>
-      <c r="K438" s="7" t="s">
-        <v>904</v>
       </c>
       <c r="L438">
         <v>308754</v>
@@ -16914,7 +16910,7 @@
         <v>13</v>
       </c>
       <c r="C439" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D439" t="s">
         <v>15</v>
@@ -16923,10 +16919,10 @@
         <v>16</v>
       </c>
       <c r="J439" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="K439" s="7" t="s">
         <v>905</v>
-      </c>
-      <c r="K439" s="7" t="s">
-        <v>906</v>
       </c>
       <c r="L439">
         <v>308754</v>
@@ -16943,7 +16939,7 @@
         <v>13</v>
       </c>
       <c r="C440" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D440" t="s">
         <v>15</v>
@@ -16952,10 +16948,10 @@
         <v>16</v>
       </c>
       <c r="J440" s="12" t="s">
+        <v>906</v>
+      </c>
+      <c r="K440" s="7" t="s">
         <v>907</v>
-      </c>
-      <c r="K440" s="7" t="s">
-        <v>908</v>
       </c>
       <c r="L440">
         <v>542809</v>
@@ -16972,7 +16968,7 @@
         <v>13</v>
       </c>
       <c r="C441" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D441" t="s">
         <v>15</v>
@@ -16981,10 +16977,10 @@
         <v>16</v>
       </c>
       <c r="J441" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="K441" s="7" t="s">
         <v>909</v>
-      </c>
-      <c r="K441" s="7" t="s">
-        <v>910</v>
       </c>
       <c r="L441">
         <v>308754</v>
@@ -17001,7 +16997,7 @@
         <v>13</v>
       </c>
       <c r="C442" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D442" t="s">
         <v>15</v>
@@ -17010,10 +17006,10 @@
         <v>16</v>
       </c>
       <c r="J442" s="12" t="s">
+        <v>910</v>
+      </c>
+      <c r="K442" s="7" t="s">
         <v>911</v>
-      </c>
-      <c r="K442" s="7" t="s">
-        <v>912</v>
       </c>
       <c r="L442">
         <v>308754</v>
@@ -17030,7 +17026,7 @@
         <v>13</v>
       </c>
       <c r="C443" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D443" t="s">
         <v>15</v>
@@ -17039,10 +17035,10 @@
         <v>16</v>
       </c>
       <c r="J443" s="12" t="s">
+        <v>912</v>
+      </c>
+      <c r="K443" s="7" t="s">
         <v>913</v>
-      </c>
-      <c r="K443" s="7" t="s">
-        <v>914</v>
       </c>
       <c r="L443">
         <v>308754</v>
@@ -17059,7 +17055,7 @@
         <v>13</v>
       </c>
       <c r="C444" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D444" t="s">
         <v>15</v>
@@ -17068,10 +17064,10 @@
         <v>16</v>
       </c>
       <c r="J444" s="12" t="s">
+        <v>914</v>
+      </c>
+      <c r="K444" s="7" t="s">
         <v>915</v>
-      </c>
-      <c r="K444" s="7" t="s">
-        <v>916</v>
       </c>
       <c r="L444">
         <v>308754</v>
@@ -17088,7 +17084,7 @@
         <v>13</v>
       </c>
       <c r="C445" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D445" t="s">
         <v>15</v>
@@ -17097,10 +17093,10 @@
         <v>16</v>
       </c>
       <c r="J445" s="12" t="s">
+        <v>916</v>
+      </c>
+      <c r="K445" s="7" t="s">
         <v>917</v>
-      </c>
-      <c r="K445" s="7" t="s">
-        <v>918</v>
       </c>
       <c r="L445">
         <v>542809</v>
@@ -17117,7 +17113,7 @@
         <v>13</v>
       </c>
       <c r="C446" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D446" t="s">
         <v>15</v>
@@ -17126,10 +17122,10 @@
         <v>16</v>
       </c>
       <c r="J446" s="12" t="s">
+        <v>918</v>
+      </c>
+      <c r="K446" s="7" t="s">
         <v>919</v>
-      </c>
-      <c r="K446" s="7" t="s">
-        <v>920</v>
       </c>
       <c r="L446">
         <v>308754</v>
@@ -17146,7 +17142,7 @@
         <v>13</v>
       </c>
       <c r="C447" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D447" t="s">
         <v>15</v>
@@ -17155,10 +17151,10 @@
         <v>16</v>
       </c>
       <c r="J447" s="12" t="s">
+        <v>920</v>
+      </c>
+      <c r="K447" s="7" t="s">
         <v>921</v>
-      </c>
-      <c r="K447" s="7" t="s">
-        <v>922</v>
       </c>
       <c r="L447">
         <v>308754</v>
@@ -17168,6 +17164,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M447" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <conditionalFormatting sqref="J306:J307">
     <cfRule type="top10" dxfId="0" priority="1" percent="1" rank="10"/>
   </conditionalFormatting>

--- a/database/db/prueba5_registros_CRCSC.xlsx
+++ b/database/db/prueba5_registros_CRCSC.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$447</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$F$1:$N$447</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3140" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3136" uniqueCount="923">
   <si>
     <t>company_id</t>
   </si>
@@ -2727,9 +2727,6 @@
   </si>
   <si>
     <t>GENERICO5111</t>
-  </si>
-  <si>
-    <t>18/03/2025</t>
   </si>
   <si>
     <t>CRSC101932</t>
@@ -2808,13 +2805,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -3662,7 +3660,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -18144,8 +18142,8 @@
       <c r="M435" s="34">
         <v>45735</v>
       </c>
-      <c r="N435" s="36" t="s">
-        <v>899</v>
+      <c r="N435" s="36">
+        <v>45734</v>
       </c>
     </row>
     <row r="436" spans="1:14">
@@ -18165,10 +18163,10 @@
         <v>17</v>
       </c>
       <c r="J436" s="35" t="s">
+        <v>899</v>
+      </c>
+      <c r="K436" s="8" t="s">
         <v>900</v>
-      </c>
-      <c r="K436" s="8" t="s">
-        <v>901</v>
       </c>
       <c r="L436">
         <v>308754</v>
@@ -18176,8 +18174,8 @@
       <c r="M436" s="34">
         <v>45735</v>
       </c>
-      <c r="N436" s="36" t="s">
-        <v>899</v>
+      <c r="N436" s="36">
+        <v>45734</v>
       </c>
     </row>
     <row r="437" spans="1:14">
@@ -18197,10 +18195,10 @@
         <v>17</v>
       </c>
       <c r="J437" s="35" t="s">
+        <v>901</v>
+      </c>
+      <c r="K437" s="8" t="s">
         <v>902</v>
-      </c>
-      <c r="K437" s="8" t="s">
-        <v>903</v>
       </c>
       <c r="L437">
         <v>542809</v>
@@ -18208,8 +18206,8 @@
       <c r="M437" s="34">
         <v>45735</v>
       </c>
-      <c r="N437" s="36" t="s">
-        <v>899</v>
+      <c r="N437" s="36">
+        <v>45734</v>
       </c>
     </row>
     <row r="438" spans="1:14">
@@ -18229,10 +18227,10 @@
         <v>17</v>
       </c>
       <c r="J438" s="35" t="s">
+        <v>903</v>
+      </c>
+      <c r="K438" s="8" t="s">
         <v>904</v>
-      </c>
-      <c r="K438" s="8" t="s">
-        <v>905</v>
       </c>
       <c r="L438">
         <v>308754</v>
@@ -18240,8 +18238,8 @@
       <c r="M438" s="34">
         <v>45735</v>
       </c>
-      <c r="N438" s="36" t="s">
-        <v>899</v>
+      <c r="N438" s="36">
+        <v>45734</v>
       </c>
     </row>
     <row r="439" spans="1:14">
@@ -18261,10 +18259,10 @@
         <v>17</v>
       </c>
       <c r="J439" s="15" t="s">
+        <v>905</v>
+      </c>
+      <c r="K439" s="8" t="s">
         <v>906</v>
-      </c>
-      <c r="K439" s="8" t="s">
-        <v>907</v>
       </c>
       <c r="L439">
         <v>308754</v>
@@ -18293,10 +18291,10 @@
         <v>17</v>
       </c>
       <c r="J440" s="15" t="s">
+        <v>907</v>
+      </c>
+      <c r="K440" s="8" t="s">
         <v>908</v>
-      </c>
-      <c r="K440" s="8" t="s">
-        <v>909</v>
       </c>
       <c r="L440">
         <v>542809</v>
@@ -18325,10 +18323,10 @@
         <v>17</v>
       </c>
       <c r="J441" s="15" t="s">
+        <v>909</v>
+      </c>
+      <c r="K441" s="8" t="s">
         <v>910</v>
-      </c>
-      <c r="K441" s="8" t="s">
-        <v>911</v>
       </c>
       <c r="L441">
         <v>308754</v>
@@ -18357,10 +18355,10 @@
         <v>17</v>
       </c>
       <c r="J442" s="15" t="s">
+        <v>911</v>
+      </c>
+      <c r="K442" s="8" t="s">
         <v>912</v>
-      </c>
-      <c r="K442" s="8" t="s">
-        <v>913</v>
       </c>
       <c r="L442">
         <v>308754</v>
@@ -18389,10 +18387,10 @@
         <v>17</v>
       </c>
       <c r="J443" s="15" t="s">
+        <v>913</v>
+      </c>
+      <c r="K443" s="8" t="s">
         <v>914</v>
-      </c>
-      <c r="K443" s="8" t="s">
-        <v>915</v>
       </c>
       <c r="L443">
         <v>308754</v>
@@ -18421,10 +18419,10 @@
         <v>17</v>
       </c>
       <c r="J444" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="K444" s="8" t="s">
         <v>916</v>
-      </c>
-      <c r="K444" s="8" t="s">
-        <v>917</v>
       </c>
       <c r="L444">
         <v>308754</v>
@@ -18453,10 +18451,10 @@
         <v>17</v>
       </c>
       <c r="J445" s="15" t="s">
+        <v>917</v>
+      </c>
+      <c r="K445" s="8" t="s">
         <v>918</v>
-      </c>
-      <c r="K445" s="8" t="s">
-        <v>919</v>
       </c>
       <c r="L445">
         <v>542809</v>
@@ -18485,10 +18483,10 @@
         <v>17</v>
       </c>
       <c r="J446" s="15" t="s">
+        <v>919</v>
+      </c>
+      <c r="K446" s="8" t="s">
         <v>920</v>
-      </c>
-      <c r="K446" s="8" t="s">
-        <v>921</v>
       </c>
       <c r="L446">
         <v>308754</v>
@@ -18517,10 +18515,10 @@
         <v>17</v>
       </c>
       <c r="J447" s="15" t="s">
+        <v>921</v>
+      </c>
+      <c r="K447" s="8" t="s">
         <v>922</v>
-      </c>
-      <c r="K447" s="8" t="s">
-        <v>923</v>
       </c>
       <c r="L447">
         <v>308754</v>
@@ -18533,7 +18531,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M447" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="F1:N447" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="J306:J307">
